--- a/plans/wbs/otter-shield-wbs-final.xlsx
+++ b/plans/wbs/otter-shield-wbs-final.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 1-39" sheetId="1" r:id="R526bae6381da4f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 40-73" sheetId="2" r:id="Rd45ba8a368eb402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세실행" sheetId="3" r:id="R8f6a21c5d3724828"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경·인계" sheetId="4" r:id="Re108d49fbacd469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 시간계획" sheetId="5" r:id="R78c0165d754e4c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 1-39" sheetId="1" r:id="Rcae57fce70ac4122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 40-73" sheetId="2" r:id="R8db0252826384566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세실행" sheetId="3" r:id="Ra6fec01c64234159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경·인계" sheetId="4" r:id="Rc6fa07c5508843f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 시간계획" sheetId="5" r:id="R7649f3accf6b4237"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -121,7 +121,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="18">
+  <x:fills count="21">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -208,6 +208,21 @@
         <x:fgColor rgb="FFFFF4D8"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDDEDE9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE1ECDD"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="6">
     <x:border>
@@ -290,7 +305,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="99">
+  <x:cellXfs count="105">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -540,6 +555,24 @@
     <x:xf numFmtId="202" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="17" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="18" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="19" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="20" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="20" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -551,7 +584,7 @@
         <x:color rgb="FF9A302B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE1DF"/>
         </x:patternFill>
       </x:fill>
@@ -561,7 +594,7 @@
         <x:color rgb="FF805A1D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF1D5"/>
         </x:patternFill>
       </x:fill>
@@ -572,7 +605,7 @@
         <x:color rgb="FF9A302B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE1DF"/>
         </x:patternFill>
       </x:fill>
@@ -3351,40 +3384,40 @@
         <x:v>M3 홍은서</x:v>
       </x:c>
       <x:c r="D8" s="50" t="n">
-        <x:v>46330</x:v>
+        <x:v>46331</x:v>
       </x:c>
       <x:c r="E8" s="49" t="str">
         <x:v>미확인</x:v>
       </x:c>
-      <x:c r="F8" s="29"/>
-      <x:c r="G8" s="29"/>
-      <x:c r="H8" s="29"/>
-      <x:c r="I8" s="29"/>
-      <x:c r="J8" s="29"/>
-      <x:c r="K8" s="33"/>
-      <x:c r="L8" s="33"/>
-      <x:c r="M8" s="29"/>
-      <x:c r="N8" s="29"/>
-      <x:c r="O8" s="29"/>
-      <x:c r="P8" s="29"/>
-      <x:c r="Q8" s="29"/>
-      <x:c r="R8" s="33"/>
-      <x:c r="S8" s="33"/>
-      <x:c r="T8" s="29"/>
-      <x:c r="U8" s="29"/>
-      <x:c r="V8" s="31"/>
-      <x:c r="W8" s="29"/>
-      <x:c r="X8" s="29"/>
-      <x:c r="Y8" s="33"/>
-      <x:c r="Z8" s="33"/>
-      <x:c r="AA8" s="29"/>
-      <x:c r="AB8" s="29"/>
-      <x:c r="AC8" s="29"/>
-      <x:c r="AD8" s="29"/>
-      <x:c r="AE8" s="29"/>
-      <x:c r="AF8" s="33"/>
-      <x:c r="AG8" s="33"/>
-      <x:c r="AH8" s="29"/>
+      <x:c r="F8" s="99"/>
+      <x:c r="G8" s="99"/>
+      <x:c r="H8" s="99"/>
+      <x:c r="I8" s="99"/>
+      <x:c r="J8" s="99"/>
+      <x:c r="K8" s="99"/>
+      <x:c r="L8" s="99"/>
+      <x:c r="M8" s="99"/>
+      <x:c r="N8" s="99"/>
+      <x:c r="O8" s="99"/>
+      <x:c r="P8" s="99"/>
+      <x:c r="Q8" s="99"/>
+      <x:c r="R8" s="99"/>
+      <x:c r="S8" s="99"/>
+      <x:c r="T8" s="99"/>
+      <x:c r="U8" s="99"/>
+      <x:c r="V8" s="101"/>
+      <x:c r="W8" s="102"/>
+      <x:c r="X8" s="99"/>
+      <x:c r="Y8" s="99"/>
+      <x:c r="Z8" s="99"/>
+      <x:c r="AA8" s="99"/>
+      <x:c r="AB8" s="99"/>
+      <x:c r="AC8" s="99"/>
+      <x:c r="AD8" s="99"/>
+      <x:c r="AE8" s="99"/>
+      <x:c r="AF8" s="99"/>
+      <x:c r="AG8" s="99"/>
+      <x:c r="AH8" s="99"/>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="38" t="str">
@@ -3397,40 +3430,40 @@
         <x:v>M4 박진혁</x:v>
       </x:c>
       <x:c r="D9" s="51" t="n">
-        <x:v>46330</x:v>
+        <x:v>46331</x:v>
       </x:c>
       <x:c r="E9" s="48" t="str">
         <x:v>미확인</x:v>
       </x:c>
-      <x:c r="F9" s="29"/>
-      <x:c r="G9" s="29"/>
-      <x:c r="H9" s="29"/>
-      <x:c r="I9" s="29"/>
-      <x:c r="J9" s="29"/>
-      <x:c r="K9" s="33"/>
-      <x:c r="L9" s="33"/>
-      <x:c r="M9" s="29"/>
-      <x:c r="N9" s="29"/>
-      <x:c r="O9" s="29"/>
-      <x:c r="P9" s="29"/>
-      <x:c r="Q9" s="29"/>
-      <x:c r="R9" s="33"/>
-      <x:c r="S9" s="33"/>
-      <x:c r="T9" s="29"/>
-      <x:c r="U9" s="29"/>
-      <x:c r="V9" s="31"/>
-      <x:c r="W9" s="29"/>
-      <x:c r="X9" s="29"/>
-      <x:c r="Y9" s="33"/>
-      <x:c r="Z9" s="33"/>
-      <x:c r="AA9" s="29"/>
-      <x:c r="AB9" s="29"/>
-      <x:c r="AC9" s="29"/>
-      <x:c r="AD9" s="29"/>
-      <x:c r="AE9" s="29"/>
-      <x:c r="AF9" s="33"/>
-      <x:c r="AG9" s="33"/>
-      <x:c r="AH9" s="29"/>
+      <x:c r="F9" s="99"/>
+      <x:c r="G9" s="99"/>
+      <x:c r="H9" s="99"/>
+      <x:c r="I9" s="99"/>
+      <x:c r="J9" s="99"/>
+      <x:c r="K9" s="99"/>
+      <x:c r="L9" s="99"/>
+      <x:c r="M9" s="99"/>
+      <x:c r="N9" s="99"/>
+      <x:c r="O9" s="99"/>
+      <x:c r="P9" s="99"/>
+      <x:c r="Q9" s="99"/>
+      <x:c r="R9" s="99"/>
+      <x:c r="S9" s="99"/>
+      <x:c r="T9" s="99"/>
+      <x:c r="U9" s="99"/>
+      <x:c r="V9" s="103"/>
+      <x:c r="W9" s="104"/>
+      <x:c r="X9" s="99"/>
+      <x:c r="Y9" s="99"/>
+      <x:c r="Z9" s="99"/>
+      <x:c r="AA9" s="99"/>
+      <x:c r="AB9" s="99"/>
+      <x:c r="AC9" s="99"/>
+      <x:c r="AD9" s="99"/>
+      <x:c r="AE9" s="99"/>
+      <x:c r="AF9" s="99"/>
+      <x:c r="AG9" s="99"/>
+      <x:c r="AH9" s="99"/>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="21" t="str">
@@ -5110,7 +5143,7 @@
         <x:v>M1 주관·전원</x:v>
       </x:c>
       <x:c r="E9" s="75" t="n">
-        <x:v>46323</x:v>
+        <x:v>46324</x:v>
       </x:c>
       <x:c r="F9" s="75" t="n">
         <x:v>46324</x:v>
@@ -5245,7 +5278,7 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L12" s="74" t="str">
-        <x:v>실측 잔여 작업 시간로 11/06 이후 기능 추가 여부 결정</x:v>
+        <x:v>남은 작업의 예상 소요 시간으로 11/06 이후 기능 추가 여부 결정</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="70" customHeight="1">
@@ -6440,7 +6473,7 @@
         <x:v>M2 윤서영</x:v>
       </x:c>
       <x:c r="E44" s="75" t="n">
-        <x:v>46324</x:v>
+        <x:v>46325</x:v>
       </x:c>
       <x:c r="F44" s="75" t="n">
         <x:v>46325</x:v>
@@ -6972,7 +7005,7 @@
         <x:v>M3 홍은서</x:v>
       </x:c>
       <x:c r="E58" s="75" t="n">
-        <x:v>46323</x:v>
+        <x:v>46324</x:v>
       </x:c>
       <x:c r="F58" s="75" t="n">
         <x:v>46324</x:v>
@@ -7314,7 +7347,7 @@
         <x:v>M4 박진혁</x:v>
       </x:c>
       <x:c r="E67" s="75" t="n">
-        <x:v>46322</x:v>
+        <x:v>46323</x:v>
       </x:c>
       <x:c r="F67" s="75" t="n">
         <x:v>46323</x:v>
@@ -8042,7 +8075,7 @@
         <x:v>46325</x:v>
       </x:c>
       <x:c r="G86" s="74" t="str">
-        <x:v>M5-A03, M5-A04, M1-A15, DEV03</x:v>
+        <x:v>M5-A03, M5-A04, M1-A15, DEV03, M1-A16</x:v>
       </x:c>
       <x:c r="H86" s="74" t="str">
         <x:v>캐나다→한국 정상 업무·Test DB 시험 준비</x:v>
@@ -8057,7 +8090,7 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L86" s="74" t="str">
-        <x:v>실제 공격 기록은 11/02</x:v>
+        <x:v>M1 게시판 배포 완료 후 캐나다에서 정상 접속 확인. Test DB 경로는 M1-A15 인계 후 시험. 실제 공격 기록은 11/02</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="70" customHeight="1">
@@ -9784,13 +9817,13 @@
         <x:v>M5</x:v>
       </x:c>
       <x:c r="E132" s="75" t="n">
-        <x:v>46330</x:v>
+        <x:v>46331</x:v>
       </x:c>
       <x:c r="F132" s="75" t="n">
         <x:v>46331</x:v>
       </x:c>
       <x:c r="G132" s="74" t="str">
-        <x:v>M5-T01</x:v>
+        <x:v>M5-T01, M3-T02</x:v>
       </x:c>
       <x:c r="H132" s="74" t="str">
         <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
@@ -9805,7 +9838,7 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L132" s="74" t="str">
-        <x:v>실측 효과를 확인. 도구 설치/정책 입력만으로 효과 판정 금지</x:v>
+        <x:v>M3가 UTM3 개선 적용을 완료한 뒤 M5가 같은 조건으로 확인. M3 적용 결과·시각을 인계받고 정상 업무도 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="70" customHeight="1">
@@ -9936,7 +9969,7 @@
         <x:v>M3</x:v>
       </x:c>
       <x:c r="E136" s="75" t="n">
-        <x:v>46331</x:v>
+        <x:v>46335</x:v>
       </x:c>
       <x:c r="F136" s="75" t="n">
         <x:v>46336</x:v>
@@ -9957,7 +9990,7 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L136" s="74" t="str">
-        <x:v>ESXi Host 1대는 전체 Host HA가 아님. Nginx B/VIP는 자원·남은 작업 시간 판정 후 적용</x:v>
+        <x:v>11/05–06 시험 절차·대상·복구 준비, 11/09–10 실제 노드 중단·복구 시험. ESXi Host 1대의 전체 Host HA는 아님. Nginx B/VIP 적용 여부는 별도 확인</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="70" customHeight="1">
@@ -10158,7 +10191,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d10e65ebc0d4e34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc298bcad526d4b33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10330,7 +10363,7 @@
         <x:v>H04</x:v>
       </x:c>
       <x:c r="B9" s="74" t="str">
-        <x:v>10/29</x:v>
+        <x:v>10/30</x:v>
       </x:c>
       <x:c r="C9" s="74" t="str">
         <x:v>M1·M3</x:v>
@@ -10339,7 +10372,7 @@
         <x:v>M5</x:v>
       </x:c>
       <x:c r="E9" s="74" t="str">
-        <x:v>일반 라우팅·격리 Test DB·원 출발지 확인</x:v>
+        <x:v>일반 라우팅·격리 Test DB·출발지 확인 결과</x:v>
       </x:c>
       <x:c r="F9" s="74" t="str">
         <x:v>M1-A15 / M3-A10</x:v>
@@ -10348,7 +10381,7 @@
         <x:v>M5-A05 / M5-S01</x:v>
       </x:c>
       <x:c r="H9" s="74" t="str">
-        <x:v>S05는 Store/AI 완료를 기다리지 않음</x:v>
+        <x:v>10/30 경로 인계 후 M5 시험. S05는 Store/AI 완료와 독립</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -10694,6 +10727,29 @@
       </x:c>
       <x:c r="G28" s="91" t="str">
         <x:v>Issue 번호·체크·댓글 보존. 증거 없으면 완료로 승격하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="90" t="n">
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="B29" s="91" t="str">
+        <x:v>일정 점검</x:v>
+      </x:c>
+      <x:c r="C29" s="91" t="str">
+        <x:v>인계표·상세 일정 일부 불일치</x:v>
+      </x:c>
+      <x:c r="D29" s="91" t="str">
+        <x:v>S05 경로 인계 10/30·노드 시험 11/09–10</x:v>
+      </x:c>
+      <x:c r="E29" s="91" t="str">
+        <x:v>선행 작업 완료 시점과 실제 시험 순서 정리</x:v>
+      </x:c>
+      <x:c r="F29" s="91" t="str">
+        <x:v>일정 표기 보완</x:v>
+      </x:c>
+      <x:c r="G29" s="91" t="str">
+        <x:v>정상 게시판 접속은 M1 배포 후, S05 개선 확인은 M3 정책 적용 후 수행</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/plans/wbs/otter-shield-wbs-final.xlsx
+++ b/plans/wbs/otter-shield-wbs-final.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 1-39" sheetId="1" r:id="Rcae57fce70ac4122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 40-73" sheetId="2" r:id="R8db0252826384566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세실행" sheetId="3" r:id="Ra6fec01c64234159"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경·인계" sheetId="4" r:id="Rc6fa07c5508843f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 시간계획" sheetId="5" r:id="R7649f3accf6b4237"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 1-39" sheetId="1" r:id="R5b89153fa64d4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 40-73" sheetId="2" r:id="R834d835b6b9c4983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세실행" sheetId="3" r:id="R8f368debc82648cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경·인계" sheetId="4" r:id="Ra14247cc2a3a47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 시간계획" sheetId="5" r:id="R89b8c8358b9444da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -615,7 +615,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActionTasks" displayName="ActionTasks" ref="A5:L141" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ActionTasks" displayName="ActionTasks" ref="A5:L143" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="실행 ID"/>
     <x:tableColumn id="2" name="단계"/>
@@ -905,7 +905,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>2026.10.26 개정 · AS-IS 10/30 · 후속 개발 일정은 PM 조정안</x:v>
+        <x:v>2026.10.26 개정 · 10/30 기본 구축·최소 테스트 인수 · 후속 기능은 별도 일정</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -1686,7 +1686,7 @@
         <x:v>I24</x:v>
       </x:c>
       <x:c r="B18" s="43" t="str">
-        <x:v>ESXi 내부 K8s·DB·OTT 경로 구성</x:v>
+        <x:v>ESXi·K8s·DB·OTT 최소 테스트·미디어 경로</x:v>
       </x:c>
       <x:c r="C18" s="44" t="str">
         <x:v>M3 홍은서</x:v>
@@ -1870,7 +1870,7 @@
         <x:v>D3</x:v>
       </x:c>
       <x:c r="B22" s="43" t="str">
-        <x:v>OTT 로그인·목록·샘플 재생 최소 인계</x:v>
+        <x:v>OTT 최소 실행본·계정/데이터·테스트 인계</x:v>
       </x:c>
       <x:c r="C22" s="44" t="str">
         <x:v>M5 유은혜</x:v>
@@ -3057,7 +3057,7 @@
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>2026.10.26 개정 · AS-IS 10/30 · 후속 개발 일정은 PM 조정안</x:v>
+        <x:v>2026.10.26 개정 · 10/30 기본 구축·최소 테스트 인수 · 후속 기능은 별도 일정</x:v>
       </x:c>
       <x:c r="B2" s="3"/>
       <x:c r="C2" s="3"/>
@@ -3746,7 +3746,7 @@
         <x:v>C8</x:v>
       </x:c>
       <x:c r="B16" s="43" t="str">
-        <x:v>AI 포함 앱·세션·배포 최종 통합 확인</x:v>
+        <x:v>DEV18 앱·자막·세션·배포 최종 인수</x:v>
       </x:c>
       <x:c r="C16" s="44" t="str">
         <x:v>M5 유은혜</x:v>
@@ -5015,7 +5015,7 @@
         <x:v>실행 시 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="70" customHeight="1">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
       <x:c r="A6" s="76" t="str">
         <x:v>C01</x:v>
       </x:c>
@@ -5034,9 +5034,7 @@
       <x:c r="F6" s="75" t="n">
         <x:v>46322</x:v>
       </x:c>
-      <x:c r="G6" s="74" t="str">
-        <x:v>독립 착수</x:v>
-      </x:c>
+      <x:c r="G6" s="74" t="str"/>
       <x:c r="H6" s="74" t="str">
         <x:v>망별 남은 작업·차단 요인 목록</x:v>
       </x:c>
@@ -5053,7 +5051,7 @@
         <x:v>10/26 회의 사용자 보고·GitHub PNG/Issue 대조. 실제 설치 검증은 담당 수행</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="70" customHeight="1">
+    <x:row r="7" ht="24" hidden="0" customHeight="1">
       <x:c r="A7" s="76" t="str">
         <x:v>C02</x:v>
       </x:c>
@@ -5088,10 +5086,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L7" s="74" t="str">
-        <x:v>M4는 확정된 OPS/REPLICA/BACKUP/PROXY 설계로 AS-IS 구축. 기존 Issue의 Replica TO-BE 문구 수정</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="70" customHeight="1">
+        <x:v>M4는 확정된 OPS/REPLICA/BACKUP/PROXY 설계로 AS-IS 구축. 확정된 4구간에서 실제 연결·기동 순서 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="76" t="str">
         <x:v>C03</x:v>
       </x:c>
@@ -5129,7 +5127,7 @@
         <x:v>상세 주소와 비밀값은 팀 기술서. 교실망/Pod/Service/AWS 중복 대조</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="70" customHeight="1">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="76" t="str">
         <x:v>C04</x:v>
       </x:c>
@@ -5167,7 +5165,7 @@
         <x:v>VPN Up과 서비스 성공을 분리. 상대 대기 중 독립 구축 계속</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="70" customHeight="1">
+    <x:row r="10" ht="36" hidden="0" customHeight="1">
       <x:c r="A10" s="76" t="str">
         <x:v>C05</x:v>
       </x:c>
@@ -5190,7 +5188,7 @@
         <x:v>M1-A18, M2-A18, M3-A13, M4-A18, M5-A06</x:v>
       </x:c>
       <x:c r="H10" s="74" t="str">
-        <x:v>망별 성공/실패·근거·인계 상태·초기 스냅샷</x:v>
+        <x:v>망별 기본 통신·필수 서비스·보안 시험 준비·최소 앱 테스트·인계 결과·초기 스냅샷</x:v>
       </x:c>
       <x:c r="I10" s="74" t="str">
         <x:v>11/02 공격 담당</x:v>
@@ -5202,10 +5200,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L10" s="74" t="str">
-        <x:v>10/30은 팀 합의 마감. 실패 항목은 완료 처리하지 않고 범위/후속 영향 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="70" customHeight="1">
+        <x:v>10/30은 AS-IS 기본 인프라와 보안 시험에 필요한 최소 앱·계정·데이터·경로의 인수일입니다. 최종 AS-IS 도면의 구성은 유지하며, AI 자막·다중 Pod 세션·AWS Store 전체 연동은 후속 일정에서 완료 여부를 확인합니다. 미달 항목은 담당·영향·재시험 기한을 기록합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="76" t="str">
         <x:v>C06</x:v>
       </x:c>
@@ -5243,7 +5241,7 @@
         <x:v>문서 길이보다 인계 가능 여부 우선. M5 PM 시간은 개발시간과 별도 확보</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="70" customHeight="1">
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
       <x:c r="A12" s="76" t="str">
         <x:v>C07</x:v>
       </x:c>
@@ -5266,7 +5264,7 @@
         <x:v>DEV06, M5-A07</x:v>
       </x:c>
       <x:c r="H12" s="74" t="str">
-        <x:v>필수 유지·후속 목표·보류 기능·AWS 사용 가능 여부</x:v>
+        <x:v>10/30 최소 앱 테스트 결과·미달 작업/영향·예상 소요·AWS 사용 가능 여부·후속 기능 우선순위</x:v>
       </x:c>
       <x:c r="I12" s="74" t="str">
         <x:v>전원</x:v>
@@ -5278,10 +5276,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L12" s="74" t="str">
-        <x:v>남은 작업의 예상 소요 시간으로 11/06 이후 기능 추가 여부 결정</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="70" customHeight="1">
+        <x:v>10/30 최소 테스트 목표 유지. 10/28 중간 실행 결과와 예상 소요 시간을 먼저 점검하고 미달 위험을 배포 담당에게 즉시 공유</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="77" t="str">
         <x:v>M1-A01</x:v>
       </x:c>
@@ -5319,7 +5317,7 @@
         <x:v>기존 UTM 설치·관리 접속 보고 보존</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="70" customHeight="1">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="77" t="str">
         <x:v>M1-A02</x:v>
       </x:c>
@@ -5357,7 +5355,7 @@
         <x:v>M5의 종단 미도달 보고 해소가 VPN 선행</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="70" customHeight="1">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="77" t="str">
         <x:v>M1-A03</x:v>
       </x:c>
@@ -5395,7 +5393,7 @@
         <x:v>130/131/132/150. VMnet과 VLAN 번호 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="70" customHeight="1">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="77" t="str">
         <x:v>M1-A04</x:v>
       </x:c>
@@ -5433,7 +5431,7 @@
         <x:v>같은 L3에서 라우팅되는 VLAN 간 트래픽은 UTM을 안 거칠 수 있음</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="70" customHeight="1">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="77" t="str">
         <x:v>M1-A05</x:v>
       </x:c>
@@ -5471,7 +5469,7 @@
         <x:v>마케팅·공통망 10/25 성공 보고. 나머지 부서 개별 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="70" customHeight="1">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="77" t="str">
         <x:v>M1-A06</x:v>
       </x:c>
@@ -5506,10 +5504,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L18" s="74" t="str">
-        <x:v>토폴로지 고정 .100과 DHCP 할당 보고 차이 대조</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="70" customHeight="1">
+        <x:v>최종 도면의 고정/동적 주소 지정과 실제 임대 결과 대조</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
       <x:c r="A19" s="77" t="str">
         <x:v>M1-A07</x:v>
       </x:c>
@@ -5547,7 +5545,7 @@
         <x:v>DNS 서버 주소 배포와 레코드 조회를 분리</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="70" customHeight="1">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
       <x:c r="A20" s="77" t="str">
         <x:v>M1-A08</x:v>
       </x:c>
@@ -5585,7 +5583,7 @@
         <x:v>Samba 읽기 전용 기존 성공 보고는 재설치하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="70" customHeight="1">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
       <x:c r="A21" s="77" t="str">
         <x:v>M1-A09</x:v>
       </x:c>
@@ -5623,7 +5621,7 @@
         <x:v>기존 10대 서버 구성 유지. M4 DR와 본사 로컬 백업 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="70" customHeight="1">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
       <x:c r="A22" s="77" t="str">
         <x:v>M1-A10</x:v>
       </x:c>
@@ -5661,7 +5659,7 @@
         <x:v>코드 개발은 M5. M1은 설치·DB·운영 환경 담당</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="70" customHeight="1">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
       <x:c r="A23" s="77" t="str">
         <x:v>M1-A11</x:v>
       </x:c>
@@ -5699,7 +5697,7 @@
         <x:v>실제 게시판 완성으로 표시하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="70" customHeight="1">
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
       <x:c r="A24" s="77" t="str">
         <x:v>M1-A12</x:v>
       </x:c>
@@ -5737,7 +5735,7 @@
         <x:v>종단·selector·NAT 예외·반환 정책 공동 대조</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="70" customHeight="1">
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
       <x:c r="A25" s="77" t="str">
         <x:v>M1-A13</x:v>
       </x:c>
@@ -5775,7 +5773,7 @@
         <x:v>비밀값은 별도 전달. 구성 성공과 서비스 성공 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="70" customHeight="1">
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
       <x:c r="A26" s="77" t="str">
         <x:v>M1-A14</x:v>
       </x:c>
@@ -5813,7 +5811,7 @@
         <x:v>본사–서비스 VPN으로 변경하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="70" customHeight="1">
+    <x:row r="27" ht="15" hidden="0" customHeight="1">
       <x:c r="A27" s="77" t="str">
         <x:v>M1-A15</x:v>
       </x:c>
@@ -5851,7 +5849,7 @@
         <x:v>허용된 격리 시험만. 운영 DB/RDS 제외</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="70" customHeight="1">
+    <x:row r="28" ht="15" hidden="0" customHeight="1">
       <x:c r="A28" s="77" t="str">
         <x:v>M1-A16</x:v>
       </x:c>
@@ -5889,7 +5887,7 @@
         <x:v>한국 설정 적용. 앱 수정 요청은 재현 로그로 M5 인계</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="70" customHeight="1">
+    <x:row r="29" ht="15" hidden="0" customHeight="1">
       <x:c r="A29" s="77" t="str">
         <x:v>M1-A17</x:v>
       </x:c>
@@ -5927,7 +5925,7 @@
         <x:v>계정·OS·시험 횟수 비교표. 공격 실행은 11/02</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="70" customHeight="1">
+    <x:row r="30" ht="24" hidden="0" customHeight="1">
       <x:c r="A30" s="77" t="str">
         <x:v>M1-A18</x:v>
       </x:c>
@@ -5965,7 +5963,7 @@
         <x:v>대표 PC 하나의 성공을 전체 부서 완료로 처리하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="70" customHeight="1">
+    <x:row r="31" ht="15" hidden="0" customHeight="1">
       <x:c r="A31" s="78" t="str">
         <x:v>M2-A01</x:v>
       </x:c>
@@ -6003,7 +6001,7 @@
         <x:v>10/23 ADMIN·방화벽/NAT 성공 보고 보존. R1 표기와 도면 R2 대조</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="70" customHeight="1">
+    <x:row r="32" ht="15" hidden="0" customHeight="1">
       <x:c r="A32" s="78" t="str">
         <x:v>M2-A02</x:v>
       </x:c>
@@ -6035,13 +6033,13 @@
         <x:v>#19</x:v>
       </x:c>
       <x:c r="K32" s="74" t="str">
-        <x:v>미확인</x:v>
+        <x:v>완료(담당 체크)</x:v>
       </x:c>
       <x:c r="L32" s="74" t="str">
         <x:v>파일 내부 TO-BE VLAN230대와 섞지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="70" customHeight="1">
+    <x:row r="33" ht="15" hidden="0" customHeight="1">
       <x:c r="A33" s="78" t="str">
         <x:v>M2-A03</x:v>
       </x:c>
@@ -6073,13 +6071,13 @@
         <x:v>#19</x:v>
       </x:c>
       <x:c r="K33" s="74" t="str">
-        <x:v>미확인</x:v>
+        <x:v>완료(담당 체크)</x:v>
       </x:c>
       <x:c r="L33" s="74" t="str">
         <x:v>직원/공통망은 L3 라우팅. UTM trunk안과 혼용 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="70" customHeight="1">
+    <x:row r="34" ht="15" hidden="0" customHeight="1">
       <x:c r="A34" s="78" t="str">
         <x:v>M2-A04</x:v>
       </x:c>
@@ -6117,7 +6115,7 @@
         <x:v>현재 AS-IS 전송 구간 기준. UTM 직접 연결 구간과 분리</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="70" customHeight="1">
+    <x:row r="35" ht="15" hidden="0" customHeight="1">
       <x:c r="A35" s="78" t="str">
         <x:v>M2-A05</x:v>
       </x:c>
@@ -6155,7 +6153,7 @@
         <x:v>다른 망 DHCP 수신 방지</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="70" customHeight="1">
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
       <x:c r="A36" s="78" t="str">
         <x:v>M2-A06</x:v>
       </x:c>
@@ -6193,7 +6191,7 @@
         <x:v>한 부서 성공으로 전체 완료 판정 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="70" customHeight="1">
+    <x:row r="37" ht="15" hidden="0" customHeight="1">
       <x:c r="A37" s="78" t="str">
         <x:v>M2-A07</x:v>
       </x:c>
@@ -6231,7 +6229,7 @@
         <x:v>한국 게시판 설정/DB와 분리</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="70" customHeight="1">
+    <x:row r="38" ht="15" hidden="0" customHeight="1">
       <x:c r="A38" s="78" t="str">
         <x:v>M2-A08</x:v>
       </x:c>
@@ -6269,7 +6267,7 @@
         <x:v>도면의 기존 업무 서버 유지</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="70" customHeight="1">
+    <x:row r="39" ht="15" hidden="0" customHeight="1">
       <x:c r="A39" s="78" t="str">
         <x:v>M2-A09</x:v>
       </x:c>
@@ -6307,7 +6305,7 @@
         <x:v>Wazuh 설치 완료와 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="70" customHeight="1">
+    <x:row r="40" ht="15" hidden="0" customHeight="1">
       <x:c r="A40" s="78" t="str">
         <x:v>M2-A10</x:v>
       </x:c>
@@ -6345,7 +6343,7 @@
         <x:v>동일 게시판 코드 사용. 앱 코드를 M2에 배정하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="70" customHeight="1">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="78" t="str">
         <x:v>M2-A11</x:v>
       </x:c>
@@ -6383,7 +6381,7 @@
         <x:v>임시 페이지는 경로 확인용</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="70" customHeight="1">
+    <x:row r="42" ht="15" hidden="0" customHeight="1">
       <x:c r="A42" s="78" t="str">
         <x:v>M2-A12</x:v>
       </x:c>
@@ -6421,7 +6419,7 @@
         <x:v>양단 확인. 한국과 독일 DB는 독립 유지</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="70" customHeight="1">
+    <x:row r="43" ht="15" hidden="0" customHeight="1">
       <x:c r="A43" s="78" t="str">
         <x:v>M2-A13</x:v>
       </x:c>
@@ -6459,7 +6457,7 @@
         <x:v>한국 데이터/계정 혼용 없음 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="70" customHeight="1">
+    <x:row r="44" ht="15" hidden="0" customHeight="1">
       <x:c r="A44" s="78" t="str">
         <x:v>M2-A14</x:v>
       </x:c>
@@ -6497,7 +6495,7 @@
         <x:v>다른 환경으로 생긴 차이를 보안 효과로 해석하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="70" customHeight="1">
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="78" t="str">
         <x:v>M2-A15</x:v>
       </x:c>
@@ -6535,7 +6533,7 @@
         <x:v>실제 반복 시험 11/02. AS-IS Wazuh 미구축</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="70" customHeight="1">
+    <x:row r="46" ht="15" hidden="0" customHeight="1">
       <x:c r="A46" s="78" t="str">
         <x:v>M2-A16</x:v>
       </x:c>
@@ -6573,7 +6571,7 @@
         <x:v>자료 준비만 병행. AS-IS 조건을 바꾸는 대응 정책 적용 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="70" customHeight="1">
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="78" t="str">
         <x:v>M2-A17</x:v>
       </x:c>
@@ -6611,7 +6609,7 @@
         <x:v>직원 VLAN의 UTM 경유 여부를 경로로 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="70" customHeight="1">
+    <x:row r="48" ht="15" hidden="0" customHeight="1">
       <x:c r="A48" s="78" t="str">
         <x:v>M2-A18</x:v>
       </x:c>
@@ -6649,7 +6647,7 @@
         <x:v>도면 제출과 실구축 완료 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="70" customHeight="1">
+    <x:row r="49" ht="15" hidden="0" customHeight="1">
       <x:c r="A49" s="79" t="str">
         <x:v>M3-A01</x:v>
       </x:c>
@@ -6687,7 +6685,7 @@
         <x:v>도면의 관리망과 별도 노드망 연결을 생략하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="70" customHeight="1">
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="79" t="str">
         <x:v>M3-A02</x:v>
       </x:c>
@@ -6725,7 +6723,7 @@
         <x:v>10/23 설치 보고 보존. 설계 변경 영향만 재확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="70" customHeight="1">
+    <x:row r="51" ht="15" hidden="0" customHeight="1">
       <x:c r="A51" s="79" t="str">
         <x:v>M3-A03</x:v>
       </x:c>
@@ -6763,7 +6761,7 @@
         <x:v>관리 API 인증 우회와 포트 도달 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="70" customHeight="1">
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="79" t="str">
         <x:v>M3-A04</x:v>
       </x:c>
@@ -6801,7 +6799,7 @@
         <x:v>Pod/Service CIDR 중복 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="70" customHeight="1">
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="79" t="str">
         <x:v>M3-A05</x:v>
       </x:c>
@@ -6839,7 +6837,7 @@
         <x:v>애플리케이션 완성을 기다리지 않고 DB 준비</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="70" customHeight="1">
+    <x:row r="54" ht="15" hidden="0" customHeight="1">
       <x:c r="A54" s="79" t="str">
         <x:v>M3-A06</x:v>
       </x:c>
@@ -6877,7 +6875,7 @@
         <x:v>SNAT로 시험 출발지가 가려지지 않는지 대조</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="70" customHeight="1">
+    <x:row r="55" ht="15" hidden="0" customHeight="1">
       <x:c r="A55" s="79" t="str">
         <x:v>M3-A07</x:v>
       </x:c>
@@ -6915,7 +6913,7 @@
         <x:v>비밀값 별도 전달. 공동 작업은 예약된 시각에 수행</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="70" customHeight="1">
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="79" t="str">
         <x:v>M3-A08</x:v>
       </x:c>
@@ -6953,7 +6951,7 @@
         <x:v>Timeout을 경로/정책/리스닝/계정으로 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="70" customHeight="1">
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="79" t="str">
         <x:v>M3-A09</x:v>
       </x:c>
@@ -6991,7 +6989,7 @@
         <x:v>임시 앱을 OTT 완성으로 표시하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="70" customHeight="1">
+    <x:row r="58" ht="15" hidden="0" customHeight="1">
       <x:c r="A58" s="79" t="str">
         <x:v>M3-A10</x:v>
       </x:c>
@@ -7029,7 +7027,7 @@
         <x:v>운영 DB·RDS를 취약 시험 대상으로 쓰지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="70" customHeight="1">
+    <x:row r="59" ht="24" hidden="0" customHeight="1">
       <x:c r="A59" s="79" t="str">
         <x:v>M3-A11</x:v>
       </x:c>
@@ -7052,7 +7050,7 @@
         <x:v>M3-A09, DEV06</x:v>
       </x:c>
       <x:c r="H59" s="74" t="str">
-        <x:v>목록·샘플 재생·DB 연동 실제 결과</x:v>
+        <x:v>목록·샘플 재생·로그인·DB 조회/저장·FastAPI 상태 응답·Redis 연결 확인</x:v>
       </x:c>
       <x:c r="I59" s="74" t="str">
         <x:v>M5</x:v>
@@ -7064,10 +7062,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L59" s="74" t="str">
-        <x:v>앱 미인계 시 임시 경로 성공과 미완료 OTT 분리</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="70" customHeight="1">
+        <x:v>10/30 최소 실행/연결 테스트. 자막 생성·재생은 DEV13/14, 다중 Pod 세션은 DEV15, 최종 통합은 DEV18에서 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="15" hidden="0" customHeight="1">
       <x:c r="A60" s="79" t="str">
         <x:v>M3-A12</x:v>
       </x:c>
@@ -7105,7 +7103,7 @@
         <x:v>공동 지원 시간과 M3 자체 작업 겹치지 않게 조정</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="70" customHeight="1">
+    <x:row r="61" ht="24" hidden="0" customHeight="1">
       <x:c r="A61" s="79" t="str">
         <x:v>M3-A13</x:v>
       </x:c>
@@ -7125,7 +7123,7 @@
         <x:v>46325</x:v>
       </x:c>
       <x:c r="G61" s="74" t="str">
-        <x:v>M3-A10, M3-A11, M3-A12</x:v>
+        <x:v>M3-A10, M3-A11, M3-A12, M3-A14</x:v>
       </x:c>
       <x:c r="H61" s="74" t="str">
         <x:v>서비스·관리·Test DB·백업 정상 결과·스냅샷</x:v>
@@ -7140,10 +7138,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L61" s="74" t="str">
-        <x:v>멀티 Pod·VIP 개선 시험은 TO-BE로 분리</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="70" customHeight="1">
+        <x:v>10/30 인수는 기본 인프라·보안 시험 준비·최소 앱 테스트 범위. 최종 도면의 AI·세션 기능은 DEV18까지 추적</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="15" hidden="0" customHeight="1">
       <x:c r="A62" s="80" t="str">
         <x:v>M4-A01</x:v>
       </x:c>
@@ -7178,10 +7176,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L62" s="74" t="str">
-        <x:v>기존 설정·성공 보고 삭제 금지. 운영/시험 PC 주소 이동 확인</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="70" customHeight="1">
+        <x:v>기존 완료 기록 유지. 최종 OPS 구간에서 운영/시험 PC 연결 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="15" hidden="0" customHeight="1">
       <x:c r="A63" s="80" t="str">
         <x:v>M4-A02</x:v>
       </x:c>
@@ -7216,10 +7214,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L63" s="74" t="str">
-        <x:v>별도 UTM GW 장비 없음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="70" customHeight="1">
+        <x:v>최종 도면의 UTM4 인터페이스를 각 구간의 GW로 사용</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="15" hidden="0" customHeight="1">
       <x:c r="A64" s="80" t="str">
         <x:v>M4-A03</x:v>
       </x:c>
@@ -7257,7 +7255,7 @@
         <x:v>시험 PC는 예전 BACKUP 동일망에서 OPS로 이동</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="70" customHeight="1">
+    <x:row r="65" ht="15" hidden="0" customHeight="1">
       <x:c r="A65" s="80" t="str">
         <x:v>M4-A04</x:v>
       </x:c>
@@ -7295,7 +7293,7 @@
         <x:v>32GB 자원 검토. 미가동 VM은 준비/검증 시 기동 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="70" customHeight="1">
+    <x:row r="66" ht="15" hidden="0" customHeight="1">
       <x:c r="A66" s="80" t="str">
         <x:v>M4-A05</x:v>
       </x:c>
@@ -7330,10 +7328,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L66" s="74" t="str">
-        <x:v>최신 4구간 PNG VPN 계획 기준. 이전 일반 라우팅 페이지와 혼용 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="70" customHeight="1">
+        <x:v>최종 M3·M4 도면의 VPN 연결 기준</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="15" hidden="0" customHeight="1">
       <x:c r="A67" s="80" t="str">
         <x:v>M4-A06</x:v>
       </x:c>
@@ -7371,7 +7369,7 @@
         <x:v>10/22 준비 보고 보존. 새 구간에서 재확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="70" customHeight="1">
+    <x:row r="68" ht="15" hidden="0" customHeight="1">
       <x:c r="A68" s="80" t="str">
         <x:v>M4-A07</x:v>
       </x:c>
@@ -7409,7 +7407,7 @@
         <x:v>같은 파일·계정으로 전후 비교 가능하게 준비</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="70" customHeight="1">
+    <x:row r="69" ht="15" hidden="0" customHeight="1">
       <x:c r="A69" s="80" t="str">
         <x:v>M4-A08</x:v>
       </x:c>
@@ -7447,7 +7445,7 @@
         <x:v>망 이동 후 파일 권한 취약점이 재현 가능한지 사전 확인. 실측 전 성공 단정 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="70" customHeight="1">
+    <x:row r="70" ht="15" hidden="0" customHeight="1">
       <x:c r="A70" s="80" t="str">
         <x:v>M4-A09</x:v>
       </x:c>
@@ -7485,7 +7483,7 @@
         <x:v>확정된 AS-IS 작업. 초기 동기화와 실제 변경 데이터 수신을 각각 확인</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="70" customHeight="1">
+    <x:row r="71" ht="15" hidden="0" customHeight="1">
       <x:c r="A71" s="80" t="str">
         <x:v>M4-A10</x:v>
       </x:c>
@@ -7523,7 +7521,7 @@
         <x:v>복제 성공은 백업 파일 생성 성공과 별개</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="70" customHeight="1">
+    <x:row r="72" ht="15" hidden="0" customHeight="1">
       <x:c r="A72" s="80" t="str">
         <x:v>M4-A11</x:v>
       </x:c>
@@ -7561,7 +7559,7 @@
         <x:v>운영 Primary 덮어쓰기 금지. 파일 일치와 DB 복원 성공 분리</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="70" customHeight="1">
+    <x:row r="73" ht="15" hidden="0" customHeight="1">
       <x:c r="A73" s="80" t="str">
         <x:v>M4-A12</x:v>
       </x:c>
@@ -7599,7 +7597,7 @@
         <x:v>자동 장애조치·자동 승격을 기본 범위로 추가하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="70" customHeight="1">
+    <x:row r="74" ht="15" hidden="0" customHeight="1">
       <x:c r="A74" s="80" t="str">
         <x:v>M4-A13</x:v>
       </x:c>
@@ -7637,7 +7635,7 @@
         <x:v>SQL 중계와 복제 기능 구분. 관리 포트는 일반 업무용 아님</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="70" customHeight="1">
+    <x:row r="75" ht="15" hidden="0" customHeight="1">
       <x:c r="A75" s="80" t="str">
         <x:v>M4-A14</x:v>
       </x:c>
@@ -7672,10 +7670,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L75" s="74" t="str">
-        <x:v>새 PNG에서 빠졌지만 기존 회의의 원격 사본 목표 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="70" customHeight="1">
+        <x:v>전체망 AS-IS 도면의 M4 백업용 S3 원격 사본</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="15" hidden="0" customHeight="1">
       <x:c r="A76" s="80" t="str">
         <x:v>M4-A15</x:v>
       </x:c>
@@ -7713,7 +7711,7 @@
         <x:v>권한 미확보는 미완료. 가짜 파일 시험과 실제 DB 덤프 결과 구분</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="70" customHeight="1">
+    <x:row r="77" ht="15" hidden="0" customHeight="1">
       <x:c r="A77" s="80" t="str">
         <x:v>M4-A16</x:v>
       </x:c>
@@ -7751,7 +7749,7 @@
         <x:v>UTM 통신 실패를 파일 권한 개선 효과로 오인하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="70" customHeight="1">
+    <x:row r="78" ht="15" hidden="0" customHeight="1">
       <x:c r="A78" s="80" t="str">
         <x:v>M4-A17</x:v>
       </x:c>
@@ -7789,7 +7787,7 @@
         <x:v>실측 RPO/RTO는 이후 시험. 임의 목표 달성 선언 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="70" customHeight="1">
+    <x:row r="79" ht="15" hidden="0" customHeight="1">
       <x:c r="A79" s="80" t="str">
         <x:v>M4-A18</x:v>
       </x:c>
@@ -7824,10 +7822,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L79" s="74" t="str">
-        <x:v>이전 토폴로지 체크 상태를 새 4구간 완료로 승계하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="70" customHeight="1">
+        <x:v>최종 4구간에서 실제 구축·동작을 확인한 항목만 완료 처리</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="15" hidden="0" customHeight="1">
       <x:c r="A80" s="80" t="str">
         <x:v>M4-A19</x:v>
       </x:c>
@@ -7865,7 +7863,7 @@
         <x:v>Gateway/Interface Endpoint 또는 NAT 선택을 실제 계정 조건으로 확정</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="70" customHeight="1">
+    <x:row r="81" ht="15" hidden="0" customHeight="1">
       <x:c r="A81" s="80" t="str">
         <x:v>M4-A20</x:v>
       </x:c>
@@ -7903,7 +7901,7 @@
         <x:v>로컬 복원과 AWS 복원을 별도 실적으로 기록</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="70" customHeight="1">
+    <x:row r="82" ht="15" hidden="0" customHeight="1">
       <x:c r="A82" s="81" t="str">
         <x:v>M5-A01</x:v>
       </x:c>
@@ -7941,7 +7939,7 @@
         <x:v>10/23 완료 보고 보존. 실제 실행은 이번에 재수행하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="70" customHeight="1">
+    <x:row r="83" ht="15" hidden="0" customHeight="1">
       <x:c r="A83" s="81" t="str">
         <x:v>M5-A02</x:v>
       </x:c>
@@ -7979,7 +7977,7 @@
         <x:v>M1-A02 미달이면 Blocked, 개발은 독립 진행</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="70" customHeight="1">
+    <x:row r="84" ht="15" hidden="0" customHeight="1">
       <x:c r="A84" s="81" t="str">
         <x:v>M5-A03</x:v>
       </x:c>
@@ -8017,7 +8015,7 @@
         <x:v>M1 주관 양단 지원. M5 가용시간 안에서 예약</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="70" customHeight="1">
+    <x:row r="85" ht="15" hidden="0" customHeight="1">
       <x:c r="A85" s="81" t="str">
         <x:v>M5-A04</x:v>
       </x:c>
@@ -8055,7 +8053,7 @@
         <x:v>운영 DB/RDS와 별도</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="70" customHeight="1">
+    <x:row r="86" ht="24" hidden="0" customHeight="1">
       <x:c r="A86" s="81" t="str">
         <x:v>M5-A05</x:v>
       </x:c>
@@ -8093,7 +8091,7 @@
         <x:v>M1 게시판 배포 완료 후 캐나다에서 정상 접속 확인. Test DB 경로는 M1-A15 인계 후 시험. 실제 공격 기록은 11/02</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="70" customHeight="1">
+    <x:row r="87" ht="24" hidden="0" customHeight="1">
       <x:c r="A87" s="81" t="str">
         <x:v>M5-A06</x:v>
       </x:c>
@@ -8128,10 +8126,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L87" s="74" t="str">
-        <x:v>사무실 완료와 AWS Store 완료를 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="70" customHeight="1">
+        <x:v>10/30 사무실망·VPN·게시판 정상 접속·Test DB 시험 준비 인수. AWS Store 전체 연동은 DEV08~10, 최종 앱 확인은 DEV18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="15" hidden="0" customHeight="1">
       <x:c r="A88" s="81" t="str">
         <x:v>M5-A07</x:v>
       </x:c>
@@ -8169,7 +8167,7 @@
         <x:v>크레딧 확보는 EKS 이용 가능 증거가 아님. 제한 지속 시 대안 일정 승인</x:v>
       </x:c>
     </x:row>
-    <x:row r="89" ht="70" customHeight="1">
+    <x:row r="89" ht="24" hidden="0" customHeight="1">
       <x:c r="A89" s="81" t="str">
         <x:v>DEV01</x:v>
       </x:c>
@@ -8204,10 +8202,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L89" s="74" t="str">
-        <x:v>D1 체크 완료 보존. 게시판 백엔드 코드 존재는 기능 완료 증거가 아님</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="70" customHeight="1">
+        <x:v>10/30 최소 테스트 가능 상태를 목표로 기존 실행본·미구현 기능·예상 소요 시간을 점검. D1 완료 체크 유지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="24" hidden="0" customHeight="1">
       <x:c r="A90" s="81" t="str">
         <x:v>DEV02</x:v>
       </x:c>
@@ -8230,7 +8228,7 @@
         <x:v>DEV01</x:v>
       </x:c>
       <x:c r="H90" s="74" t="str">
-        <x:v>공통 코드·로그인·기본 CRUD·DB 저장 자체 확인</x:v>
+        <x:v>공통 게시판 로그인·기본 CRUD·DB 저장 자체 테스트</x:v>
       </x:c>
       <x:c r="I90" s="74" t="str">
         <x:v>M1·M2</x:v>
@@ -8242,10 +8240,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L90" s="74" t="str">
-        <x:v>새 디자인·부가기능 제외. 기존 코드가 실행 가능하다는 조건</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="70" customHeight="1">
+        <x:v>10/28 인계 목표, 10/30 실제 환경 최소 테스트. 기존 코드 재사용·가짜 데이터 우선, 화면 고도화 제외</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="15" hidden="0" customHeight="1">
       <x:c r="A91" s="81" t="str">
         <x:v>DEV03</x:v>
       </x:c>
@@ -8283,7 +8281,7 @@
         <x:v>배포는 M1/M2. 인계 후 소스 변경 시 버전 재전달</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="70" customHeight="1">
+    <x:row r="92" ht="24" hidden="0" customHeight="1">
       <x:c r="A92" s="81" t="str">
         <x:v>DEV04</x:v>
       </x:c>
@@ -8306,7 +8304,7 @@
         <x:v>DEV01</x:v>
       </x:c>
       <x:c r="H92" s="74" t="str">
-        <x:v>하나의 샘플 영상과 콘텐츠 목록·DB 연동</x:v>
+        <x:v>샘플 영상·콘텐츠 목록·DB 조회·미디어 파일/URL 규격</x:v>
       </x:c>
       <x:c r="I92" s="74" t="str">
         <x:v>M3</x:v>
@@ -8318,10 +8316,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L92" s="74" t="str">
-        <x:v>영상은 기존 샘플 사용. 신규 스트리밍 엔진 제외</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="70" customHeight="1">
+        <x:v>M5는 10/29 샘플과 URL 규격을 M3에 인계. M3-A14에서 CloudFront 영상 경로 확인. 신규 스트리밍 엔진 제외</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="15" hidden="0" customHeight="1">
       <x:c r="A93" s="81" t="str">
         <x:v>DEV05</x:v>
       </x:c>
@@ -8359,7 +8357,7 @@
         <x:v>기본 권한 기능 유지. 자동 통합로그인 범위 제외</x:v>
       </x:c>
     </x:row>
-    <x:row r="94" ht="70" customHeight="1">
+    <x:row r="94" ht="24" hidden="0" customHeight="1">
       <x:c r="A94" s="81" t="str">
         <x:v>DEV06</x:v>
       </x:c>
@@ -8382,7 +8380,7 @@
         <x:v>DEV05</x:v>
       </x:c>
       <x:c r="H94" s="74" t="str">
-        <x:v>이미지/실행본·DDL·환경변수·정상 URL</x:v>
+        <x:v>OTT 최소 실행본·DDL·가짜 계정/데이터·실행 명령·정상 URL·FastAPI 상태 확인 규격</x:v>
       </x:c>
       <x:c r="I94" s="74" t="str">
         <x:v>M3</x:v>
@@ -8394,10 +8392,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L94" s="74" t="str">
-        <x:v>첫 실제 배포는 M3. 기능 미달 시 완료 처리 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="70" customHeight="1">
+        <x:v>10/30 M3 실제 환경의 최소 테스트가 목표. FastAPI 실제 자막 생성은 DEV13 이후 별도 확인. 테스트 미실행은 완료 처리하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="15" hidden="0" customHeight="1">
       <x:c r="A95" s="81" t="str">
         <x:v>DEV07</x:v>
       </x:c>
@@ -8435,7 +8433,7 @@
         <x:v>주말 총 가용 8h 가정. 실제 결제·장바구니 고도화 제외</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="70" customHeight="1">
+    <x:row r="96" ht="15" hidden="0" customHeight="1">
       <x:c r="A96" s="81" t="str">
         <x:v>DEV08</x:v>
       </x:c>
@@ -8473,7 +8471,7 @@
         <x:v>계정 제약 해소 조건. CloudFormation 범위는 기존 준비파일 재사용 우선</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="70" customHeight="1">
+    <x:row r="97" ht="15" hidden="0" customHeight="1">
       <x:c r="A97" s="81" t="str">
         <x:v>DEV09</x:v>
       </x:c>
@@ -8511,7 +8509,7 @@
         <x:v>인증서·도메인은 DEV10에서 확인. 로컬 성공을 AWS 성공으로 표시하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="98" ht="70" customHeight="1">
+    <x:row r="98" ht="15" hidden="0" customHeight="1">
       <x:c r="A98" s="81" t="str">
         <x:v>DEV10</x:v>
       </x:c>
@@ -8549,7 +8547,7 @@
         <x:v>DNS 전파 대기 중 다른 독립 작업 수행</x:v>
       </x:c>
     </x:row>
-    <x:row r="99" ht="70" customHeight="1">
+    <x:row r="99" ht="15" hidden="0" customHeight="1">
       <x:c r="A99" s="81" t="str">
         <x:v>DEV11</x:v>
       </x:c>
@@ -8587,7 +8585,7 @@
         <x:v>착수 전까지 보류 유지. 날짜는 PM 목표이며 미리 도구 확정 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="100" ht="70" customHeight="1">
+    <x:row r="100" ht="15" hidden="0" customHeight="1">
       <x:c r="A100" s="81" t="str">
         <x:v>DEV12</x:v>
       </x:c>
@@ -8625,7 +8623,7 @@
         <x:v>M3는 클러스터 적용 협업. 두 사이트 자동화가 미달이면 범위 조정 기록</x:v>
       </x:c>
     </x:row>
-    <x:row r="101" ht="70" customHeight="1">
+    <x:row r="101" ht="15" hidden="0" customHeight="1">
       <x:c r="A101" s="81" t="str">
         <x:v>DEV13</x:v>
       </x:c>
@@ -8663,7 +8661,7 @@
         <x:v>외부 API 사전 시험 성공 조건. 모의 응답을 실제 생성으로 표시 금지</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="70" customHeight="1">
+    <x:row r="102" ht="24" hidden="0" customHeight="1">
       <x:c r="A102" s="81" t="str">
         <x:v>DEV14</x:v>
       </x:c>
@@ -8683,7 +8681,7 @@
         <x:v>46334</x:v>
       </x:c>
       <x:c r="G102" s="74" t="str">
-        <x:v>DEV13, M3-A11</x:v>
+        <x:v>DEV13, M3-A11, M3-A14</x:v>
       </x:c>
       <x:c r="H102" s="74" t="str">
         <x:v>직접 생성한 자막을 플레이어에서 재생</x:v>
@@ -8698,10 +8696,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L102" s="74" t="str">
-        <x:v>주말 총8h 가정. 프랑스어·챗봇·실시간 처리 보류</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="70" customHeight="1">
+        <x:v>M5 코드·자막 파일/URL 인계 후 M3가 실제 배포. 자막 파일 조회와 플레이어 선택·재생 확인. 주말 합계8h 가정, 최종 인수 DEV18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="15" hidden="0" customHeight="1">
       <x:c r="A103" s="81" t="str">
         <x:v>DEV15</x:v>
       </x:c>
@@ -8739,7 +8737,7 @@
         <x:v>서비스별 별도 Redis. Redis 자체 HA·다른 도메인 SSO는 별도</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="70" customHeight="1">
+    <x:row r="104" ht="15" hidden="0" customHeight="1">
       <x:c r="A104" s="81" t="str">
         <x:v>DEV16</x:v>
       </x:c>
@@ -8777,7 +8775,7 @@
         <x:v>11/06은 중간 확인, AI 포함 최종 통합 목표는 11/09로 분리</x:v>
       </x:c>
     </x:row>
-    <x:row r="105" ht="70" customHeight="1">
+    <x:row r="105" ht="24" hidden="0" customHeight="1">
       <x:c r="A105" s="81" t="str">
         <x:v>DEV17</x:v>
       </x:c>
@@ -8797,7 +8795,7 @@
         <x:v>46336</x:v>
       </x:c>
       <x:c r="G105" s="74" t="str">
-        <x:v>DEV10, DEV16</x:v>
+        <x:v>DEV10, DEV18</x:v>
       </x:c>
       <x:c r="H105" s="74" t="str">
         <x:v>새 RDS로 복원·접속 변경·대표 데이터 조회·정리</x:v>
@@ -8812,10 +8810,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L105" s="74" t="str">
-        <x:v>원본 RDS 덮어쓰기 금지. 단순 스냅샷 생성으로 완료 처리 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="70" customHeight="1">
+        <x:v>11/09 DEV18 정상 앱 기준선을 인계받은 뒤 격리 복원 시작. 원본 RDS 덮어쓰기 금지. 스냅샷 생성만으로 완료 처리 금지</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="24" hidden="0" customHeight="1">
       <x:c r="A106" s="77" t="str">
         <x:v>M1-S01</x:v>
       </x:c>
@@ -8838,10 +8836,10 @@
         <x:v>M1-A18</x:v>
       </x:c>
       <x:c r="H106" s="74" t="str">
-        <x:v>조건·실제 결과·원본 로그·원인 분석</x:v>
+        <x:v>직원/관리자별 TCP 도달·SSH 인증 결과·UTM/서버 로그·실제 경유 경로</x:v>
       </x:c>
       <x:c r="I106" s="74" t="str">
-        <x:v>PL 및 개선 담당</x:v>
+        <x:v>PL·M1 개선 담당</x:v>
       </x:c>
       <x:c r="J106" s="74" t="str">
         <x:v>#15</x:v>
@@ -8850,10 +8848,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L106" s="74" t="str">
-        <x:v>10/30 AS-IS 인수 후 실행. 실패/미재현 결과도 사실대로 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="70" customHeight="1">
+        <x:v>UTM 경유 여부·서버 수신·호스트 정책·계정 정책을 구분. L3 내부 경로라면 UTM만으로 통제 가능하다고 단정하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="15" hidden="0" customHeight="1">
       <x:c r="A107" s="77" t="str">
         <x:v>M1-T01</x:v>
       </x:c>
@@ -8876,7 +8874,7 @@
         <x:v>M1-S01</x:v>
       </x:c>
       <x:c r="H107" s="74" t="str">
-        <x:v>전후 설계·정책 근거·검증 방법</x:v>
+        <x:v>허용/차단 대상·통제 위치·변경 설정·정상 업무·검증/되돌리기 조건표</x:v>
       </x:c>
       <x:c r="I107" s="74" t="str">
         <x:v>PL</x:v>
@@ -8888,10 +8886,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L107" s="74" t="str">
-        <x:v>M5 S05는 M3 설정 소유. 앱 코드를 다른 망 담당에게 배정하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="70" customHeight="1">
+        <x:v>직원 관리 접근 차단·승인 관리자 유지. 실제 경로에 맞는 통제 위치 선정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="24" hidden="0" customHeight="1">
       <x:c r="A108" s="77" t="str">
         <x:v>M1-T02</x:v>
       </x:c>
@@ -8914,7 +8912,7 @@
         <x:v>M1-T01</x:v>
       </x:c>
       <x:c r="H108" s="74" t="str">
-        <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
+        <x:v>직원 관리 접근 차단·승인 관리자 유지. 실제 경로에 맞는 통제 위치 선정 및 변경 전후 실제 결과</x:v>
       </x:c>
       <x:c r="I108" s="74" t="str">
         <x:v>공동 시험 담당</x:v>
@@ -8926,10 +8924,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L108" s="74" t="str">
-        <x:v>실측 효과를 확인. 도구 설치/정책 입력만으로 효과 판정 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="70" customHeight="1">
+        <x:v>UTM 경유 여부·서버 수신·호스트 정책·계정 정책을 구분. L3 내부 경로라면 UTM만으로 통제 가능하다고 단정하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="15" hidden="0" customHeight="1">
       <x:c r="A109" s="77" t="str">
         <x:v>M1-T03</x:v>
       </x:c>
@@ -8952,7 +8950,7 @@
         <x:v>M1-T02</x:v>
       </x:c>
       <x:c r="H109" s="74" t="str">
-        <x:v>보안·정상 업무 결과·미해결 항목</x:v>
+        <x:v>게시판·DNS·Samba·승인 관리자 SSH의 실제 정상 결과·미해결 항목</x:v>
       </x:c>
       <x:c r="I109" s="74" t="str">
         <x:v>PM·PL</x:v>
@@ -8964,10 +8962,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L109" s="74" t="str">
-        <x:v>AI 포함 앱 최종 인수 목표는 11/09. 인프라 개선 확인과 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="70" customHeight="1">
+        <x:v>11/06은 보안 개선·정상 업무 중간 확인. 전체 앱 최종 인수는 DEV18(11/09)에서 공동 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="24" hidden="0" customHeight="1">
       <x:c r="A110" s="77" t="str">
         <x:v>M1-R01</x:v>
       </x:c>
@@ -8990,7 +8988,7 @@
         <x:v>M1-T03</x:v>
       </x:c>
       <x:c r="H110" s="74" t="str">
-        <x:v>전/후 비교·정상 업무·실패 원인·확인자</x:v>
+        <x:v>개선 전후 동일 조건의 직원/관리자별 TCP 도달·SSH 인증 결과·UTM/서버 로그·실제 경유 경로 및 정상 업무 결과</x:v>
       </x:c>
       <x:c r="I110" s="74" t="str">
         <x:v>보고서 담당</x:v>
@@ -9002,10 +9000,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L110" s="74" t="str">
-        <x:v>출발지·계정·대상·횟수 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="70" customHeight="1">
+        <x:v>같은 WAS·시험 계정·포트에서 직원과 관리자 출발지를 구분. 차단 성공과 정상 업무 유지 결과를 별도로 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="15" hidden="0" customHeight="1">
       <x:c r="A111" s="77" t="str">
         <x:v>M1-F01</x:v>
       </x:c>
@@ -9043,7 +9041,7 @@
         <x:v>자기 망 기술서는 각 담당이 작성. PM이 전부 대필하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="70" customHeight="1">
+    <x:row r="112" ht="15" hidden="0" customHeight="1">
       <x:c r="A112" s="78" t="str">
         <x:v>M2-S01</x:v>
       </x:c>
@@ -9066,10 +9064,10 @@
         <x:v>M2-A18</x:v>
       </x:c>
       <x:c r="H112" s="74" t="str">
-        <x:v>조건·실제 결과·원본 로그·원인 분석</x:v>
+        <x:v>합의한 반복 인증 실패·서버 원본 인증 로그·시각·출발지·계정·횟수</x:v>
       </x:c>
       <x:c r="I112" s="74" t="str">
-        <x:v>PL 및 개선 담당</x:v>
+        <x:v>PL·M2 개선 담당</x:v>
       </x:c>
       <x:c r="J112" s="74" t="str">
         <x:v>#20</x:v>
@@ -9078,10 +9076,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L112" s="74" t="str">
-        <x:v>10/30 AS-IS 인수 후 실행. 실패/미재현 결과도 사실대로 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="70" customHeight="1">
+        <x:v>Wazuh 미설치 AS-IS 원본을 보존. 시험 횟수/간격 제한과 정상 계정 잠금 영향 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="15" hidden="0" customHeight="1">
       <x:c r="A113" s="78" t="str">
         <x:v>M2-T01</x:v>
       </x:c>
@@ -9104,7 +9102,7 @@
         <x:v>M2-S01</x:v>
       </x:c>
       <x:c r="H113" s="74" t="str">
-        <x:v>전후 설계·정책 근거·검증 방법</x:v>
+        <x:v>허용/차단 대상·통제 위치·변경 설정·정상 업무·검증/되돌리기 조건표</x:v>
       </x:c>
       <x:c r="I113" s="74" t="str">
         <x:v>PL</x:v>
@@ -9116,10 +9114,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L113" s="74" t="str">
-        <x:v>M5 S05는 M3 설정 소유. 앱 코드를 다른 망 담당에게 배정하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="70" customHeight="1">
+        <x:v>Wazuh Agent→수집→탐지→선정 대응→해제 순서와 실행 주체·복구 조건 결정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="24" hidden="0" customHeight="1">
       <x:c r="A114" s="78" t="str">
         <x:v>M2-T02</x:v>
       </x:c>
@@ -9142,7 +9140,7 @@
         <x:v>M2-T01</x:v>
       </x:c>
       <x:c r="H114" s="74" t="str">
-        <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
+        <x:v>Wazuh Agent→수집→탐지→선정 대응→해제 순서와 실행 주체·복구 조건 결정 및 변경 전후 실제 결과</x:v>
       </x:c>
       <x:c r="I114" s="74" t="str">
         <x:v>공동 시험 담당</x:v>
@@ -9154,10 +9152,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L114" s="74" t="str">
-        <x:v>실측 효과를 확인. 도구 설치/정책 입력만으로 효과 판정 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="70" customHeight="1">
+        <x:v>Wazuh 미설치 AS-IS 원본을 보존. 시험 횟수/간격 제한과 정상 계정 잠금 영향 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="15" hidden="0" customHeight="1">
       <x:c r="A115" s="78" t="str">
         <x:v>M2-T03</x:v>
       </x:c>
@@ -9180,7 +9178,7 @@
         <x:v>M2-T02</x:v>
       </x:c>
       <x:c r="H115" s="74" t="str">
-        <x:v>보안·정상 업무 결과·미해결 항목</x:v>
+        <x:v>독일 게시판·승인 SSH·파일 업무·로그 수집의 실제 정상 결과·미해결 항목</x:v>
       </x:c>
       <x:c r="I115" s="74" t="str">
         <x:v>PM·PL</x:v>
@@ -9192,10 +9190,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L115" s="74" t="str">
-        <x:v>AI 포함 앱 최종 인수 목표는 11/09. 인프라 개선 확인과 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="70" customHeight="1">
+        <x:v>11/06은 보안 개선·정상 업무 중간 확인. 전체 앱 최종 인수는 DEV18(11/09)에서 공동 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="24" hidden="0" customHeight="1">
       <x:c r="A116" s="78" t="str">
         <x:v>M2-R01</x:v>
       </x:c>
@@ -9218,7 +9216,7 @@
         <x:v>M2-T03</x:v>
       </x:c>
       <x:c r="H116" s="74" t="str">
-        <x:v>전/후 비교·정상 업무·실패 원인·확인자</x:v>
+        <x:v>개선 전후 동일 조건의 합의한 반복 인증 실패·서버 원본 인증 로그·시각·출발지·계정·횟수 및 정상 업무 결과</x:v>
       </x:c>
       <x:c r="I116" s="74" t="str">
         <x:v>보고서 담당</x:v>
@@ -9230,10 +9228,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L116" s="74" t="str">
-        <x:v>출발지·계정·대상·횟수 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" ht="70" customHeight="1">
+        <x:v>M1과 비교할 OS·계정 정책·시도 횟수·간격·정상 관리자 조건을 고정. 차단 성공과 정상 업무 유지 결과를 별도로 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="15" hidden="0" customHeight="1">
       <x:c r="A117" s="78" t="str">
         <x:v>M2-F01</x:v>
       </x:c>
@@ -9271,7 +9269,7 @@
         <x:v>자기 망 기술서는 각 담당이 작성. PM이 전부 대필하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="70" customHeight="1">
+    <x:row r="118" ht="15" hidden="0" customHeight="1">
       <x:c r="A118" s="79" t="str">
         <x:v>M3-S01</x:v>
       </x:c>
@@ -9294,10 +9292,10 @@
         <x:v>M3-A13</x:v>
       </x:c>
       <x:c r="H118" s="74" t="str">
-        <x:v>조건·실제 결과·원본 로그·원인 분석</x:v>
+        <x:v>TCP/TLS 도달·HTTP/인증 결과·승인 관리자 요청 결과·UTM/API 로그</x:v>
       </x:c>
       <x:c r="I118" s="74" t="str">
-        <x:v>PL 및 개선 담당</x:v>
+        <x:v>PL·M3 개선 담당</x:v>
       </x:c>
       <x:c r="J118" s="74" t="str">
         <x:v>#25</x:v>
@@ -9306,10 +9304,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L118" s="74" t="str">
-        <x:v>10/30 AS-IS 인수 후 실행. 실패/미재현 결과도 사실대로 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="70" customHeight="1">
+        <x:v>포트 도달만으로 인증 우회·클러스터 제어 성공으로 판정하지 않음. 승인된 비파괴 조회만 수행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="24" hidden="0" customHeight="1">
       <x:c r="A119" s="79" t="str">
         <x:v>M3-T01</x:v>
       </x:c>
@@ -9329,10 +9327,10 @@
         <x:v>46329</x:v>
       </x:c>
       <x:c r="G119" s="74" t="str">
-        <x:v>M3-S01</x:v>
+        <x:v>M3-S01, M5-S01</x:v>
       </x:c>
       <x:c r="H119" s="74" t="str">
-        <x:v>전후 설계·정책 근거·검증 방법</x:v>
+        <x:v>S03 관리 API와 S05 Test DB의 허용/차단 출발지·대상·포트·정책 위치·정상 업무·롤백 표</x:v>
       </x:c>
       <x:c r="I119" s="74" t="str">
         <x:v>PL</x:v>
@@ -9344,10 +9342,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L119" s="74" t="str">
-        <x:v>M5 S05는 M3 설정 소유. 앱 코드를 다른 망 담당에게 배정하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" ht="70" customHeight="1">
+        <x:v>M5의 S05 결과·출발지·UTM3 로그를 인계받고 M3가 UTM3 변경안을 작성. M5가 다른 담당의 설정을 임의 변경하지 않음</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="24" hidden="0" customHeight="1">
       <x:c r="A120" s="79" t="str">
         <x:v>M3-T02</x:v>
       </x:c>
@@ -9370,7 +9368,7 @@
         <x:v>M3-T01</x:v>
       </x:c>
       <x:c r="H120" s="74" t="str">
-        <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
+        <x:v>S03 관리 API와 S05 Test DB 경로를 함께 검토. 관리자·백업·OTT 정상 경로 유지 및 변경 전후 실제 결과</x:v>
       </x:c>
       <x:c r="I120" s="74" t="str">
         <x:v>공동 시험 담당</x:v>
@@ -9382,10 +9380,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L120" s="74" t="str">
-        <x:v>실측 효과를 확인. 도구 설치/정책 입력만으로 효과 판정 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="70" customHeight="1">
+        <x:v>포트 도달만으로 인증 우회·클러스터 제어 성공으로 판정하지 않음. 승인된 비파괴 조회만 수행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="15" hidden="0" customHeight="1">
       <x:c r="A121" s="79" t="str">
         <x:v>M3-T03</x:v>
       </x:c>
@@ -9408,7 +9406,7 @@
         <x:v>M3-T02</x:v>
       </x:c>
       <x:c r="H121" s="74" t="str">
-        <x:v>보안·정상 업무 결과·미해결 항목</x:v>
+        <x:v>OTT·승인 API/ESXi 관리·Primary 복제/백업·미디어 요청의 실제 정상 결과·미해결 항목</x:v>
       </x:c>
       <x:c r="I121" s="74" t="str">
         <x:v>PM·PL</x:v>
@@ -9420,10 +9418,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L121" s="74" t="str">
-        <x:v>AI 포함 앱 최종 인수 목표는 11/09. 인프라 개선 확인과 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="70" customHeight="1">
+        <x:v>11/06은 보안 개선·정상 업무 중간 확인. 전체 앱 최종 인수는 DEV18(11/09)에서 공동 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="24" hidden="0" customHeight="1">
       <x:c r="A122" s="79" t="str">
         <x:v>M3-R01</x:v>
       </x:c>
@@ -9446,7 +9444,7 @@
         <x:v>M3-T03</x:v>
       </x:c>
       <x:c r="H122" s="74" t="str">
-        <x:v>전/후 비교·정상 업무·실패 원인·확인자</x:v>
+        <x:v>개선 전후 동일 조건의 TCP/TLS 도달·HTTP/인증 결과·승인 관리자 요청 결과·UTM/API 로그 및 정상 업무 결과</x:v>
       </x:c>
       <x:c r="I122" s="74" t="str">
         <x:v>보고서 담당</x:v>
@@ -9458,10 +9456,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L122" s="74" t="str">
-        <x:v>출발지·계정·대상·횟수 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="70" customHeight="1">
+        <x:v>동일 API 대상에서 네트워크 도달·인증/권한·응답을 따로 기록. 차단 성공과 정상 업무 유지 결과를 별도로 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="15" hidden="0" customHeight="1">
       <x:c r="A123" s="79" t="str">
         <x:v>M3-F01</x:v>
       </x:c>
@@ -9499,7 +9497,7 @@
         <x:v>자기 망 기술서는 각 담당이 작성. PM이 전부 대필하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="70" customHeight="1">
+    <x:row r="124" ht="24" hidden="0" customHeight="1">
       <x:c r="A124" s="80" t="str">
         <x:v>M4-S01</x:v>
       </x:c>
@@ -9522,10 +9520,10 @@
         <x:v>M4-A18</x:v>
       </x:c>
       <x:c r="H124" s="74" t="str">
-        <x:v>조건·실제 결과·원본 로그·원인 분석</x:v>
+        <x:v>계정별 파일 읽기 결과·전후 해시/내용·소유권/권한·auditd/접근 로그</x:v>
       </x:c>
       <x:c r="I124" s="74" t="str">
-        <x:v>PL 및 개선 담당</x:v>
+        <x:v>PL·M4 개선 담당</x:v>
       </x:c>
       <x:c r="J124" s="74" t="str">
         <x:v>#30</x:v>
@@ -9534,10 +9532,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L124" s="74" t="str">
-        <x:v>10/30 AS-IS 인수 후 실행. 실패/미재현 결과도 사실대로 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" ht="70" customHeight="1">
+        <x:v>통신 불가와 파일 권한 거부를 구분. 실제 DB 덤프/운영 백업은 시험 대상에서 제외하고 시험 후 초기 상태 복구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="15" hidden="0" customHeight="1">
       <x:c r="A125" s="80" t="str">
         <x:v>M4-T01</x:v>
       </x:c>
@@ -9560,7 +9558,7 @@
         <x:v>M4-S01</x:v>
       </x:c>
       <x:c r="H125" s="74" t="str">
-        <x:v>전후 설계·정책 근거·검증 방법</x:v>
+        <x:v>허용/차단 대상·통제 위치·변경 설정·정상 업무·검증/되돌리기 조건표</x:v>
       </x:c>
       <x:c r="I125" s="74" t="str">
         <x:v>PL</x:v>
@@ -9572,10 +9570,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L125" s="74" t="str">
-        <x:v>M5 S05는 M3 설정 소유. 앱 코드를 다른 망 담당에게 배정하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" ht="70" customHeight="1">
+        <x:v>파일·상위 디렉터리 권한/그룹·서비스 접근·감사 설정을 실제 원인에 맞춰 변경</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="24" hidden="0" customHeight="1">
       <x:c r="A126" s="80" t="str">
         <x:v>M4-T02</x:v>
       </x:c>
@@ -9598,7 +9596,7 @@
         <x:v>M4-T01</x:v>
       </x:c>
       <x:c r="H126" s="74" t="str">
-        <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
+        <x:v>파일·상위 디렉터리 권한/그룹·서비스 접근·감사 설정을 실제 원인에 맞춰 변경 및 변경 전후 실제 결과</x:v>
       </x:c>
       <x:c r="I126" s="74" t="str">
         <x:v>공동 시험 담당</x:v>
@@ -9610,10 +9608,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L126" s="74" t="str">
-        <x:v>실측 효과를 확인. 도구 설치/정책 입력만으로 효과 판정 금지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" ht="70" customHeight="1">
+        <x:v>통신 불가와 파일 권한 거부를 구분. 실제 DB 덤프/운영 백업은 시험 대상에서 제외하고 시험 후 초기 상태 복구</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="24" hidden="0" customHeight="1">
       <x:c r="A127" s="80" t="str">
         <x:v>M4-T03</x:v>
       </x:c>
@@ -9636,7 +9634,7 @@
         <x:v>M4-T02</x:v>
       </x:c>
       <x:c r="H127" s="74" t="str">
-        <x:v>보안·정상 업무 결과·미해결 항목</x:v>
+        <x:v>정상 계정 백업/읽기·Replica 덤프·별도 DB 복원·ProxySQL 업무 조회의 실제 정상 결과·미해결 항목</x:v>
       </x:c>
       <x:c r="I127" s="74" t="str">
         <x:v>PM·PL</x:v>
@@ -9648,10 +9646,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L127" s="74" t="str">
-        <x:v>AI 포함 앱 최종 인수 목표는 11/09. 인프라 개선 확인과 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" ht="70" customHeight="1">
+        <x:v>11/06은 보안 개선·정상 업무 중간 확인. 전체 앱 최종 인수는 DEV18(11/09)에서 공동 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="24" hidden="0" customHeight="1">
       <x:c r="A128" s="80" t="str">
         <x:v>M4-R01</x:v>
       </x:c>
@@ -9674,7 +9672,7 @@
         <x:v>M4-T03</x:v>
       </x:c>
       <x:c r="H128" s="74" t="str">
-        <x:v>전/후 비교·정상 업무·실패 원인·확인자</x:v>
+        <x:v>개선 전후 동일 조건의 계정별 파일 읽기 결과·전후 해시/내용·소유권/권한·auditd/접근 로그 및 정상 업무 결과</x:v>
       </x:c>
       <x:c r="I128" s="74" t="str">
         <x:v>보고서 담당</x:v>
@@ -9686,10 +9684,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L128" s="74" t="str">
-        <x:v>출발지·계정·대상·횟수 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="70" customHeight="1">
+        <x:v>같은 파일·시험/정상 계정·서비스·초기 내용/소유권/권한을 고정. 차단 성공과 정상 업무 유지 결과를 별도로 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="15" hidden="0" customHeight="1">
       <x:c r="A129" s="80" t="str">
         <x:v>M4-F01</x:v>
       </x:c>
@@ -9727,7 +9725,7 @@
         <x:v>자기 망 기술서는 각 담당이 작성. PM이 전부 대필하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="70" customHeight="1">
+    <x:row r="130" ht="15" hidden="0" customHeight="1">
       <x:c r="A130" s="81" t="str">
         <x:v>M5-S01</x:v>
       </x:c>
@@ -9750,10 +9748,10 @@
         <x:v>M5-A06</x:v>
       </x:c>
       <x:c r="H130" s="74" t="str">
-        <x:v>조건·실제 결과·원본 로그·원인 분석</x:v>
+        <x:v>VPN/왕복 경로·UTM3에서 보이는 출발지·DB TCP/인증/가짜 조회·정상 게시판 결과</x:v>
       </x:c>
       <x:c r="I130" s="74" t="str">
-        <x:v>PL 및 개선 담당</x:v>
+        <x:v>M3 개선 담당·PL</x:v>
       </x:c>
       <x:c r="J130" s="74" t="str">
         <x:v>#35</x:v>
@@ -9762,10 +9760,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L130" s="74" t="str">
-        <x:v>10/30 AS-IS 인수 후 실행. 실패/미재현 결과도 사실대로 기록</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="70" customHeight="1">
+        <x:v>NAT로 출발지가 바뀌는지 기록. 운영 Primary/RDS와 분리하고 결과를 M3에 인계</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="15" hidden="0" customHeight="1">
       <x:c r="A131" s="81" t="str">
         <x:v>M5-T01</x:v>
       </x:c>
@@ -9788,7 +9786,7 @@
         <x:v>M5-S01</x:v>
       </x:c>
       <x:c r="H131" s="74" t="str">
-        <x:v>전후 설계·정책 근거·검증 방법</x:v>
+        <x:v>허용/차단 대상·통제 위치·변경 설정·정상 업무·검증/되돌리기 조건표</x:v>
       </x:c>
       <x:c r="I131" s="74" t="str">
         <x:v>PL</x:v>
@@ -9800,10 +9798,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L131" s="74" t="str">
-        <x:v>M5 S05는 M3 설정 소유. 앱 코드를 다른 망 담당에게 배정하지 않음</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="70" customHeight="1">
+        <x:v>M3가 UTM3 Test DB 접근 정책 적용, M5는 같은 출발지에서 차단과 정상 웹 요청 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="24" hidden="0" customHeight="1">
       <x:c r="A132" s="81" t="str">
         <x:v>M5-T02</x:v>
       </x:c>
@@ -9826,7 +9824,7 @@
         <x:v>M5-T01, M3-T02</x:v>
       </x:c>
       <x:c r="H132" s="74" t="str">
-        <x:v>실제 적용 결과·정상 업무 유지·롤백</x:v>
+        <x:v>M3가 UTM3 Test DB 접근 정책 적용, M5는 같은 출발지에서 차단과 정상 웹 요청 확인 및 변경 전후 실제 결과</x:v>
       </x:c>
       <x:c r="I132" s="74" t="str">
         <x:v>공동 시험 담당</x:v>
@@ -9838,10 +9836,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L132" s="74" t="str">
-        <x:v>M3가 UTM3 개선 적용을 완료한 뒤 M5가 같은 조건으로 확인. M3 적용 결과·시각을 인계받고 정상 업무도 확인</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="70" customHeight="1">
+        <x:v>M3-T02 적용 결과와 시각 인계 후 M5 시험. 같은 날 진행하므로 적용 완료→인계→시험 순서 예약</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="15" hidden="0" customHeight="1">
       <x:c r="A133" s="81" t="str">
         <x:v>M5-T03</x:v>
       </x:c>
@@ -9864,7 +9862,7 @@
         <x:v>M5-T02</x:v>
       </x:c>
       <x:c r="H133" s="74" t="str">
-        <x:v>보안·정상 업무 결과·미해결 항목</x:v>
+        <x:v>T15 VPN·한국 DNS/게시판·Store HTTPS/업무 요청의 실제 정상 결과·미해결 항목</x:v>
       </x:c>
       <x:c r="I133" s="74" t="str">
         <x:v>PM·PL</x:v>
@@ -9876,10 +9874,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L133" s="74" t="str">
-        <x:v>AI 포함 앱 최종 인수 목표는 11/09. 인프라 개선 확인과 구분</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" ht="70" customHeight="1">
+        <x:v>11/06은 보안 개선·정상 업무 중간 확인. 전체 앱 최종 인수는 DEV18(11/09)에서 공동 확인</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="24" hidden="0" customHeight="1">
       <x:c r="A134" s="81" t="str">
         <x:v>M5-R01</x:v>
       </x:c>
@@ -9902,7 +9900,7 @@
         <x:v>M5-T03</x:v>
       </x:c>
       <x:c r="H134" s="74" t="str">
-        <x:v>전/후 비교·정상 업무·실패 원인·확인자</x:v>
+        <x:v>개선 전후 동일 조건의 VPN/왕복 경로·UTM3에서 보이는 출발지·DB TCP/인증/가짜 조회·정상 게시판 결과 및 정상 업무 결과</x:v>
       </x:c>
       <x:c r="I134" s="74" t="str">
         <x:v>보고서 담당</x:v>
@@ -9914,10 +9912,10 @@
         <x:v>조정안</x:v>
       </x:c>
       <x:c r="L134" s="74" t="str">
-        <x:v>출발지·계정·대상·횟수 유지</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" ht="70" customHeight="1">
+        <x:v>같은 출발 PC·가짜 읽기 계정·Test DB·포트에서 시험. 정상 한국 게시판 요청을 비교. 차단 성공과 정상 업무 유지 결과를 별도로 기록</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="15" hidden="0" customHeight="1">
       <x:c r="A135" s="81" t="str">
         <x:v>M5-F01</x:v>
       </x:c>
@@ -9955,7 +9953,7 @@
         <x:v>자기 망 기술서는 각 담당이 작성. PM이 전부 대필하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="136" ht="70" customHeight="1">
+    <x:row r="136" ht="36" hidden="0" customHeight="1">
       <x:c r="A136" s="79" t="str">
         <x:v>M3-H01</x:v>
       </x:c>
@@ -9990,10 +9988,10 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L136" s="74" t="str">
-        <x:v>11/05–06 시험 절차·대상·복구 준비, 11/09–10 실제 노드 중단·복구 시험. ESXi Host 1대의 전체 Host HA는 아님. Nginx B/VIP 적용 여부는 별도 확인</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="70" customHeight="1">
+        <x:v>11/05–06 시험 절차·대상·복구 준비, 11/09–10 실제 노드 중단·복구 시험. ESXi Host 1대의 전체 Host HA는 아님. 최종 AS-IS는 Nginx 1대. Nginx B/VIP는 TO-BE 변경안에서 적용 여부를 결정</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" ht="15" hidden="0" customHeight="1">
       <x:c r="A137" s="80" t="str">
         <x:v>M4-R02</x:v>
       </x:c>
@@ -10031,7 +10029,7 @@
         <x:v>ProxySQL 자동 승격·장애조치는 필수 범위로 추가하지 않음</x:v>
       </x:c>
     </x:row>
-    <x:row r="138" ht="70" customHeight="1">
+    <x:row r="138" ht="15" hidden="0" customHeight="1">
       <x:c r="A138" s="76" t="str">
         <x:v>F01</x:v>
       </x:c>
@@ -10069,7 +10067,7 @@
         <x:v>초안은 담당이 병행 제출. 최종 취합은 증거 인계 후</x:v>
       </x:c>
     </x:row>
-    <x:row r="139" ht="70" customHeight="1">
+    <x:row r="139" ht="15" hidden="0" customHeight="1">
       <x:c r="A139" s="76" t="str">
         <x:v>F02</x:v>
       </x:c>
@@ -10105,7 +10103,7 @@
       </x:c>
       <x:c r="L139" s="74" t="str"/>
     </x:row>
-    <x:row r="140" ht="70" customHeight="1">
+    <x:row r="140" ht="15" hidden="0" customHeight="1">
       <x:c r="A140" s="76" t="str">
         <x:v>F03</x:v>
       </x:c>
@@ -10143,7 +10141,7 @@
         <x:v>주말 작업 가능자는 담당별 확인. 본 검토는 온라인 점검 위주</x:v>
       </x:c>
     </x:row>
-    <x:row r="141" ht="70" customHeight="1">
+    <x:row r="141" ht="15" hidden="0" customHeight="1">
       <x:c r="A141" s="76" t="str">
         <x:v>F04</x:v>
       </x:c>
@@ -10178,6 +10176,82 @@
         <x:v>미확인</x:v>
       </x:c>
       <x:c r="L141" s="74" t="str"/>
+    </x:row>
+    <x:row r="142" ht="100" hidden="0" customHeight="1">
+      <x:c r="A142" s="76" t="str">
+        <x:v>M3-A14</x:v>
+      </x:c>
+      <x:c r="B142" s="76" t="str">
+        <x:v>AS-IS</x:v>
+      </x:c>
+      <x:c r="C142" s="74" t="str">
+        <x:v>CloudFront·비공개 S3 샘플 영상 경로 확인</x:v>
+      </x:c>
+      <x:c r="D142" s="74" t="str">
+        <x:v>M3 홍은서·M5 유은혜 협업</x:v>
+      </x:c>
+      <x:c r="E142" s="75" t="n">
+        <x:v>46324</x:v>
+      </x:c>
+      <x:c r="F142" s="75" t="n">
+        <x:v>46325</x:v>
+      </x:c>
+      <x:c r="G142" s="74" t="str">
+        <x:v>M3-A01, DEV04</x:v>
+      </x:c>
+      <x:c r="H142" s="74" t="str">
+        <x:v>M3 미디어 S3·CloudFront 접근 설정·샘플 영상 HTTPS 응답/재생·URL 인계</x:v>
+      </x:c>
+      <x:c r="I142" s="74" t="str">
+        <x:v>M5 앱 연동·PL</x:v>
+      </x:c>
+      <x:c r="J142" s="74" t="str">
+        <x:v>#24</x:v>
+      </x:c>
+      <x:c r="K142" s="74" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="L142" s="74" t="str">
+        <x:v>최종 AS-IS 도면의 미디어 구성. M3가 버킷/배포·원본 접근 권한을 준비하고 M5가 파일·URL 규격 인계. M4 백업 S3와 분리. 실제 자막 연동은 DEV14/18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" ht="100" hidden="0" customHeight="1">
+      <x:c r="A143" s="76" t="str">
+        <x:v>DEV18</x:v>
+      </x:c>
+      <x:c r="B143" s="76" t="str">
+        <x:v>개발·AWS</x:v>
+      </x:c>
+      <x:c r="C143" s="74" t="str">
+        <x:v>게시판·OTT/AI·Store 최종 앱 인수</x:v>
+      </x:c>
+      <x:c r="D143" s="74" t="str">
+        <x:v>M5 유은혜·M1/M2/M3 배포 협업</x:v>
+      </x:c>
+      <x:c r="E143" s="75" t="n">
+        <x:v>46335</x:v>
+      </x:c>
+      <x:c r="F143" s="75" t="n">
+        <x:v>46335</x:v>
+      </x:c>
+      <x:c r="G143" s="74" t="str">
+        <x:v>DEV10, DEV14, DEV15, DEV16, M3-A14</x:v>
+      </x:c>
+      <x:c r="H143" s="74" t="str">
+        <x:v>게시판 로그인/CRUD·OTT 영상/생성 자막·세션 유지·Store 모의 주문/DB 저장·배포 버전·미달 목록</x:v>
+      </x:c>
+      <x:c r="I143" s="74" t="str">
+        <x:v>PM·PL·재검증 담당</x:v>
+      </x:c>
+      <x:c r="J143" s="74" t="str">
+        <x:v>#8</x:v>
+      </x:c>
+      <x:c r="K143" s="74" t="str">
+        <x:v>미확인</x:v>
+      </x:c>
+      <x:c r="L143" s="74" t="str">
+        <x:v>M1/M2 게시판·M3 OTT/AI·M5 Store에서 실제 요청으로 공동 확인. AI 코드/파일은 M5, M3 배포·미디어 권한은 M3. 검증 뒤 DEV17 RDS 복원에 정상 기준선 인계</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="K6:K141">
@@ -10191,7 +10265,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc298bcad526d4b33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc99d33cc1b74c38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10505,13 +10579,13 @@
         <x:v>실제 앱·자막·세션·롤백 최종 인수</x:v>
       </x:c>
       <x:c r="F14" s="74" t="str">
-        <x:v>DEV14~DEV16</x:v>
+        <x:v>DEV18</x:v>
       </x:c>
       <x:c r="G14" s="74" t="str">
-        <x:v>재검증·발표</x:v>
+        <x:v>DEV17 / 망별 재검증</x:v>
       </x:c>
       <x:c r="H14" s="74" t="str">
-        <x:v>인프라 11/06 확인과 앱 최종 인수 구분</x:v>
+        <x:v>11/09 공동 확인 후 RDS 격리 복원 시작. 미달 기능은 인수 목록에 명시</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="70" customHeight="1">
@@ -10750,6 +10824,29 @@
       </x:c>
       <x:c r="G29" s="91" t="str">
         <x:v>정상 게시판 접속은 M1 배포 후, S05 개선 확인은 M3 정책 적용 후 수행</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="24" hidden="0" customHeight="1">
+      <x:c r="A30" s="90" t="n">
+        <x:v>46321</x:v>
+      </x:c>
+      <x:c r="B30" s="91" t="str">
+        <x:v>최종 검토</x:v>
+      </x:c>
+      <x:c r="C30" s="91" t="str">
+        <x:v>AS-IS 전체 완료와 최소 테스트 혼용</x:v>
+      </x:c>
+      <x:c r="D30" s="91" t="str">
+        <x:v>10/30 최소 테스트·M3-A14·DEV18 추가</x:v>
+      </x:c>
+      <x:c r="E30" s="91" t="str">
+        <x:v>사용자 최소 테스트 목표 및 누락 인계 보완</x:v>
+      </x:c>
+      <x:c r="F30" s="91" t="str">
+        <x:v>사용자 지시 반영</x:v>
+      </x:c>
+      <x:c r="G30" s="91" t="str">
+        <x:v>S05→M3-T01 인계·망별 시험 기준 구체화</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -10888,7 +10985,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="74" t="str">
-        <x:v>기본망 대조·VPN 조건·기존 코드 실행</x:v>
+        <x:v>기존 코드 실행·미구현/예상 시간 기록·VPN 조건</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="52" customHeight="1">
@@ -10922,7 +11019,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J7" s="74" t="str">
-        <x:v>게시판 최소 기능·인계, AWS 권한 판정</x:v>
+        <x:v>게시판 최소 테스트·인계·AWS 권한·남은 시간 점검</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="52" customHeight="1">
@@ -10990,7 +11087,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J9" s="74" t="str">
-        <x:v>OTT 로그인·인계·S05 준비</x:v>
+        <x:v>OTT 최소 테스트·실제 배포 확인·S05 준비</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="52" customHeight="1">
@@ -11262,7 +11359,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J17" s="74" t="str">
-        <x:v>공동 재검증·RDS 복원·회귀</x:v>
+        <x:v>DEV18 최종 앱 인수→RDS 격리 복원·회귀</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="52" customHeight="1">
@@ -11341,9 +11438,14 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>가용시간 배분안. 개발 예상 소요는 10/27 코드 실행 후 기록하고 10/28에 최소 테스트 범위와 대조. 10/30 목표 유지.</x:v>
+      </x:c>
+    </x:row>
     <x:row r="23" ht="36" customHeight="1">
       <x:c r="A23" s="89" t="str">
-        <x:v>이 표는 확정 작업 시간가 아니라 가용시간 배분안. 모든 기능의 실측 소요가 이 안에 들어온다는 보장은 없음.</x:v>
+        <x:v>10/27–30 총8h 중 개발/AWS 배정4.5h. 10/30 게시판·OTT 최소 테스트 우선, 구현/배포 실패는 즉시 담당과 인계 조정.</x:v>
       </x:c>
       <x:c r="B23" s="89"/>
       <x:c r="C23" s="89"/>

--- a/plans/wbs/otter-shield-wbs-final.xlsx
+++ b/plans/wbs/otter-shield-wbs-final.xlsx
@@ -6,7 +6,6 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시용 40-73" sheetId="2" r:id="R834d835b6b9c4983"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상세실행" sheetId="3" r:id="R8f368debc82648cb"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변경·인계" sheetId="4" r:id="Ra14247cc2a3a47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M5 시간계획" sheetId="5" r:id="R89b8c8358b9444da"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10852,680 +10851,4 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="80" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="67"/>
-      <x:c r="B1" s="67"/>
-      <x:c r="C1" s="67"/>
-      <x:c r="D1" s="67"/>
-      <x:c r="E1" s="67"/>
-      <x:c r="F1" s="67"/>
-      <x:c r="G1" s="67"/>
-      <x:c r="H1" s="67"/>
-      <x:c r="I1" s="67"/>
-      <x:c r="J1" s="67"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="68" t="str">
-        <x:v>M5 시간계획 · 2026.10.26</x:v>
-      </x:c>
-      <x:c r="B2" s="67"/>
-      <x:c r="C2" s="67"/>
-      <x:c r="D2" s="67"/>
-      <x:c r="E2" s="67"/>
-      <x:c r="F2" s="67"/>
-      <x:c r="G2" s="67"/>
-      <x:c r="H2" s="67"/>
-      <x:c r="I2" s="67"/>
-      <x:c r="J2" s="67"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="67" t="str">
-        <x:v>PM 가정: 평일 2h·주말 묶음 합계 8h. 실제 가용시간·실제 소요 시간 확인 필요. 10/26 작업분은 소급 배정하지 않음.</x:v>
-      </x:c>
-      <x:c r="B3" s="67"/>
-      <x:c r="C3" s="67"/>
-      <x:c r="D3" s="67"/>
-      <x:c r="E3" s="67"/>
-      <x:c r="F3" s="67"/>
-      <x:c r="G3" s="67"/>
-      <x:c r="H3" s="67"/>
-      <x:c r="I3" s="67"/>
-      <x:c r="J3" s="67"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="67"/>
-      <x:c r="B4" s="67"/>
-      <x:c r="C4" s="67"/>
-      <x:c r="D4" s="67"/>
-      <x:c r="E4" s="67"/>
-      <x:c r="F4" s="67"/>
-      <x:c r="G4" s="67"/>
-      <x:c r="H4" s="67"/>
-      <x:c r="I4" s="67"/>
-      <x:c r="J4" s="67"/>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="73" t="str">
-        <x:v>기준일</x:v>
-      </x:c>
-      <x:c r="B5" s="73" t="str">
-        <x:v>가용 구분</x:v>
-      </x:c>
-      <x:c r="C5" s="73" t="str">
-        <x:v>가용 h</x:v>
-      </x:c>
-      <x:c r="D5" s="73" t="str">
-        <x:v>PM h</x:v>
-      </x:c>
-      <x:c r="E5" s="73" t="str">
-        <x:v>망·보안 h</x:v>
-      </x:c>
-      <x:c r="F5" s="73" t="str">
-        <x:v>개발·AWS h</x:v>
-      </x:c>
-      <x:c r="G5" s="73" t="str">
-        <x:v>오류 여유 h</x:v>
-      </x:c>
-      <x:c r="H5" s="73" t="str">
-        <x:v>계획 합계 h</x:v>
-      </x:c>
-      <x:c r="I5" s="73" t="str">
-        <x:v>남은 h</x:v>
-      </x:c>
-      <x:c r="J5" s="73" t="str">
-        <x:v>작업 계획</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="52" customHeight="1">
-      <x:c r="A6" s="75" t="n">
-        <x:v>46322</x:v>
-      </x:c>
-      <x:c r="B6" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C6" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="E6" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F6" s="94" t="n">
-        <x:v>0.75</x:v>
-      </x:c>
-      <x:c r="G6" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H6" s="92" t="n">
-        <x:f>SUM(D6:G6)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I6" s="92" t="n">
-        <x:f>C6-H6</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J6" s="74" t="str">
-        <x:v>기존 코드 실행·미구현/예상 시간 기록·VPN 조건</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="52" customHeight="1">
-      <x:c r="A7" s="75" t="n">
-        <x:v>46323</x:v>
-      </x:c>
-      <x:c r="B7" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C7" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E7" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F7" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G7" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H7" s="92" t="n">
-        <x:f>SUM(D7:G7)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I7" s="92" t="n">
-        <x:f>C7-H7</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J7" s="74" t="str">
-        <x:v>게시판 최소 테스트·인계·AWS 권한·남은 시간 점검</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="52" customHeight="1">
-      <x:c r="A8" s="75" t="n">
-        <x:v>46324</x:v>
-      </x:c>
-      <x:c r="B8" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C8" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E8" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F8" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G8" s="94" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="92" t="n">
-        <x:f>SUM(D8:G8)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I8" s="92" t="n">
-        <x:f>C8-H8</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J8" s="74" t="str">
-        <x:v>VPN 공동 확인·OTT 목록/재생</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="52" customHeight="1">
-      <x:c r="A9" s="75" t="n">
-        <x:v>46325</x:v>
-      </x:c>
-      <x:c r="B9" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C9" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E9" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F9" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G9" s="94" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="92" t="n">
-        <x:f>SUM(D9:G9)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I9" s="92" t="n">
-        <x:f>C9-H9</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="74" t="str">
-        <x:v>OTT 최소 테스트·실제 배포 확인·S05 준비</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="52" customHeight="1">
-      <x:c r="A10" s="75" t="n">
-        <x:v>46326</x:v>
-      </x:c>
-      <x:c r="B10" s="74" t="str">
-        <x:v>주말 묶음</x:v>
-      </x:c>
-      <x:c r="C10" s="94" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="94" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" s="94" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="94" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="G10" s="94" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="92" t="n">
-        <x:f>SUM(D10:G10)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I10" s="92" t="n">
-        <x:f>C10-H10</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J10" s="74" t="str">
-        <x:v>10/31~11/01 합계 8h 가정. Store 로컬3h+AWS기반3h</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="52" customHeight="1">
-      <x:c r="A11" s="75" t="n">
-        <x:v>46328</x:v>
-      </x:c>
-      <x:c r="B11" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C11" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="E11" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F11" s="94" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="94" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="92" t="n">
-        <x:f>SUM(D11:G11)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I11" s="92" t="n">
-        <x:f>C11-H11</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="74" t="str">
-        <x:v>S05 시험·분석·남은 AWS 오류 보완</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="52" customHeight="1">
-      <x:c r="A12" s="75" t="n">
-        <x:v>46329</x:v>
-      </x:c>
-      <x:c r="B12" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C12" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E12" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F12" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G12" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H12" s="92" t="n">
-        <x:f>SUM(D12:G12)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I12" s="92" t="n">
-        <x:f>C12-H12</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J12" s="74" t="str">
-        <x:v>TO-BE 설계·Store 초기 연결·AI 사전 시험</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="52" customHeight="1">
-      <x:c r="A13" s="75" t="n">
-        <x:v>46330</x:v>
-      </x:c>
-      <x:c r="B13" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C13" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E13" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F13" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G13" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H13" s="92" t="n">
-        <x:f>SUM(D13:G13)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I13" s="92" t="n">
-        <x:f>C13-H13</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J13" s="74" t="str">
-        <x:v>Store 연동·CI/CD 선정·AI 파일 작업</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="52" customHeight="1">
-      <x:c r="A14" s="75" t="n">
-        <x:v>46331</x:v>
-      </x:c>
-      <x:c r="B14" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C14" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E14" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F14" s="94" t="n">
-        <x:v>1.25</x:v>
-      </x:c>
-      <x:c r="G14" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H14" s="92" t="n">
-        <x:f>SUM(D14:G14)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I14" s="92" t="n">
-        <x:f>C14-H14</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J14" s="74" t="str">
-        <x:v>도메인 HTTPS·자동화 최소 경로</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="52" customHeight="1">
-      <x:c r="A15" s="75" t="n">
-        <x:v>46332</x:v>
-      </x:c>
-      <x:c r="B15" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C15" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="E15" s="94" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="F15" s="94" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G15" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="H15" s="92" t="n">
-        <x:f>SUM(D15:G15)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I15" s="92" t="n">
-        <x:f>C15-H15</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J15" s="74" t="str">
-        <x:v>인프라 개선 확인·AI 파일·자동화 중간 확인</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="52" customHeight="1">
-      <x:c r="A16" s="75" t="n">
-        <x:v>46333</x:v>
-      </x:c>
-      <x:c r="B16" s="74" t="str">
-        <x:v>주말 묶음</x:v>
-      </x:c>
-      <x:c r="C16" s="94" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D16" s="94" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E16" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F16" s="94" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G16" s="94" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="H16" s="92" t="n">
-        <x:f>SUM(D16:G16)</x:f>
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I16" s="92" t="n">
-        <x:f>C16-H16</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J16" s="74" t="str">
-        <x:v>11/07~08 합계 8h 가정. AI 웹2h·세션1.5h·통합1.5h</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="52" customHeight="1">
-      <x:c r="A17" s="75" t="n">
-        <x:v>46335</x:v>
-      </x:c>
-      <x:c r="B17" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C17" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="E17" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F17" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="G17" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="H17" s="92" t="n">
-        <x:f>SUM(D17:G17)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I17" s="92" t="n">
-        <x:f>C17-H17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J17" s="74" t="str">
-        <x:v>DEV18 최종 앱 인수→RDS 격리 복원·회귀</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="52" customHeight="1">
-      <x:c r="A18" s="75" t="n">
-        <x:v>46336</x:v>
-      </x:c>
-      <x:c r="B18" s="74" t="str">
-        <x:v>평일</x:v>
-      </x:c>
-      <x:c r="C18" s="94" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="E18" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="F18" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="G18" s="94" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="H18" s="92" t="n">
-        <x:f>SUM(D18:G18)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I18" s="92" t="n">
-        <x:f>C18-H18</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J18" s="74" t="str">
-        <x:v>재검증 보완·RDS 정리·증거</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="C19" s="93"/>
-      <x:c r="D19" s="93"/>
-      <x:c r="E19" s="93"/>
-      <x:c r="F19" s="93"/>
-      <x:c r="G19" s="93"/>
-      <x:c r="H19" s="93"/>
-      <x:c r="I19" s="93"/>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="B20" s="97" t="str">
-        <x:v>합계</x:v>
-      </x:c>
-      <x:c r="C20" s="98" t="n">
-        <x:f>SUM(C6:C18)</x:f>
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="D20" s="98" t="n">
-        <x:f>SUM(D6:D18)</x:f>
-        <x:v>5.75</x:v>
-      </x:c>
-      <x:c r="E20" s="98" t="n">
-        <x:f>SUM(E6:E18)</x:f>
-        <x:v>4.75</x:v>
-      </x:c>
-      <x:c r="F20" s="98" t="n">
-        <x:f>SUM(F6:F18)</x:f>
-        <x:v>21.25</x:v>
-      </x:c>
-      <x:c r="G20" s="98" t="n">
-        <x:f>SUM(G6:G18)</x:f>
-        <x:v>6.25</x:v>
-      </x:c>
-      <x:c r="H20" s="98" t="n">
-        <x:f>SUM(H6:H18)</x:f>
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="I20" s="98" t="n">
-        <x:f>SUM(I6:I18)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>가용시간 배분안. 개발 예상 소요는 10/27 코드 실행 후 기록하고 10/28에 최소 테스트 범위와 대조. 10/30 목표 유지.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="36" customHeight="1">
-      <x:c r="A23" s="89" t="str">
-        <x:v>10/27–30 총8h 중 개발/AWS 배정4.5h. 10/30 게시판·OTT 최소 테스트 우선, 구현/배포 실패는 즉시 담당과 인계 조정.</x:v>
-      </x:c>
-      <x:c r="B23" s="89"/>
-      <x:c r="C23" s="89"/>
-      <x:c r="D23" s="89"/>
-      <x:c r="E23" s="89"/>
-      <x:c r="F23" s="89"/>
-      <x:c r="G23" s="89"/>
-      <x:c r="H23" s="89"/>
-      <x:c r="I23" s="89"/>
-      <x:c r="J23" s="89"/>
-    </x:row>
-    <x:row r="24" ht="36" customHeight="1">
-      <x:c r="A24" s="89" t="str">
-        <x:v>10/27–30 총8h: 기존 코드가 실행 가능할 때 게시판·OTT 최소 인계 목표. 10/28 잔여 작업 시간 초과 시 같은 날 범위 재판정.</x:v>
-      </x:c>
-      <x:c r="B24" s="89"/>
-      <x:c r="C24" s="89"/>
-      <x:c r="D24" s="89"/>
-      <x:c r="E24" s="89"/>
-      <x:c r="F24" s="89"/>
-      <x:c r="G24" s="89"/>
-      <x:c r="H24" s="89"/>
-      <x:c r="I24" s="89"/>
-      <x:c r="J24" s="89"/>
-    </x:row>
-    <x:row r="25" ht="36" customHeight="1">
-      <x:c r="A25" s="89" t="str">
-        <x:v>주말은 각각 이틀 합계8h 가정. 실제 양일 모두 작업 가능하다고 가정하지 않음. 한 날짜는 묶음 시작일.</x:v>
-      </x:c>
-      <x:c r="B25" s="89"/>
-      <x:c r="C25" s="89"/>
-      <x:c r="D25" s="89"/>
-      <x:c r="E25" s="89"/>
-      <x:c r="F25" s="89"/>
-      <x:c r="G25" s="89"/>
-      <x:c r="H25" s="89"/>
-      <x:c r="I25" s="89"/>
-      <x:c r="J25" s="89"/>
-    </x:row>
-    <x:row r="26" ht="36" customHeight="1">
-      <x:c r="A26" s="89" t="str">
-        <x:v>11/06 인프라 중간 확인·11/09 AI 포함 앱 최종 인수 목표. 기능 미달 시 추가 기능보다 통합·재시험 우선.</x:v>
-      </x:c>
-      <x:c r="B26" s="89"/>
-      <x:c r="C26" s="89"/>
-      <x:c r="D26" s="89"/>
-      <x:c r="E26" s="89"/>
-      <x:c r="F26" s="89"/>
-      <x:c r="G26" s="89"/>
-      <x:c r="H26" s="89"/>
-      <x:c r="I26" s="89"/>
-      <x:c r="J26" s="89"/>
-    </x:row>
-    <x:row r="27" ht="36" customHeight="1">
-      <x:c r="A27" s="89" t="str">
-        <x:v>범위 조정 후보: 두 사이트 전체 자동화·Nginx B/VIP·전 인프라 재생성. 보류: 챗봇·프랑스어·SSO·실제 결제·자동 DB 승격.</x:v>
-      </x:c>
-      <x:c r="B27" s="89"/>
-      <x:c r="C27" s="89"/>
-      <x:c r="D27" s="89"/>
-      <x:c r="E27" s="89"/>
-      <x:c r="F27" s="89"/>
-      <x:c r="G27" s="89"/>
-      <x:c r="H27" s="89"/>
-      <x:c r="I27" s="89"/>
-      <x:c r="J27" s="89"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A23:J23"/>
-    <x:mergeCell ref="A24:J24"/>
-    <x:mergeCell ref="A25:J25"/>
-    <x:mergeCell ref="A26:J26"/>
-    <x:mergeCell ref="A27:J27"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="I6:I18">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>